--- a/examples/nort_belhaj_analysis/results/manova.xlsx
+++ b/examples/nort_belhaj_analysis/results/manova.xlsx
@@ -491,16 +491,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.1683</v>
+        <v>0.0078</v>
       </c>
       <c r="E2" t="n">
-        <v>0.583</v>
+        <v>0.9</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.7691</v>
+        <v>-0.2846</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4326</v>
+        <v>0.3003</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
@@ -521,16 +521,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.2587</v>
+        <v>-0.0815</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3945</v>
+        <v>0.5896</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.8659</v>
+        <v>-0.3775</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3485</v>
+        <v>0.2144</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
@@ -551,16 +551,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.2795</v>
+        <v>-0.147</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3464</v>
+        <v>0.3068</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3132</v>
+        <v>-0.4339</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8723</v>
+        <v>0.1398</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
@@ -581,16 +581,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.2476</v>
+        <v>0.0606</v>
       </c>
       <c r="E5" t="n">
-        <v>0.408</v>
+        <v>0.6884</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3505</v>
+        <v>-0.2312</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8457</v>
+        <v>0.3525</v>
       </c>
       <c r="H5" t="b">
         <v>0</v>
@@ -607,16 +607,16 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1864</v>
+        <v>-0.0738</v>
       </c>
       <c r="E6" t="n">
         <v>0.9</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.4813</v>
+        <v>-1.2036</v>
       </c>
       <c r="G6" t="n">
-        <v>2.1086</v>
+        <v>1.0559</v>
       </c>
       <c r="H6" t="b">
         <v>0</v>
@@ -633,16 +633,16 @@
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3588</v>
+        <v>0.0114</v>
       </c>
       <c r="E7" t="n">
         <v>0.9</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.6287</v>
+        <v>-0.967</v>
       </c>
       <c r="G7" t="n">
-        <v>2.3463</v>
+        <v>0.9898</v>
       </c>
       <c r="H7" t="b">
         <v>0</v>
@@ -659,16 +659,16 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1545</v>
+        <v>-0.1205</v>
       </c>
       <c r="E8" t="n">
         <v>0.9</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.2625</v>
+        <v>-1.1582</v>
       </c>
       <c r="G8" t="n">
-        <v>1.9536</v>
+        <v>0.9173</v>
       </c>
       <c r="H8" t="b">
         <v>0</v>
@@ -685,16 +685,16 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0349</v>
+        <v>0.0372</v>
       </c>
       <c r="E9" t="n">
         <v>0.9</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.8264</v>
+        <v>-0.8447</v>
       </c>
       <c r="G9" t="n">
-        <v>1.7566</v>
+        <v>0.9191</v>
       </c>
       <c r="H9" t="b">
         <v>0</v>
@@ -711,16 +711,16 @@
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3765</v>
+        <v>0.3481</v>
       </c>
       <c r="E10" t="n">
         <v>0.9</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.611</v>
+        <v>-0.6303</v>
       </c>
       <c r="G10" t="n">
-        <v>2.364</v>
+        <v>1.3264</v>
       </c>
       <c r="H10" t="b">
         <v>0</v>
@@ -737,16 +737,16 @@
         <v>7</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9560999999999999</v>
+        <v>0.09320000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>0.711</v>
+        <v>0.9</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.9467</v>
+        <v>-0.8435</v>
       </c>
       <c r="G11" t="n">
-        <v>2.859</v>
+        <v>1.0299</v>
       </c>
       <c r="H11" t="b">
         <v>0</v>
@@ -763,16 +763,16 @@
         <v>8</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0473</v>
+        <v>-0.2093</v>
       </c>
       <c r="E12" t="n">
         <v>0.9</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.7928</v>
+        <v>-1.1151</v>
       </c>
       <c r="G12" t="n">
-        <v>1.8873</v>
+        <v>0.6965</v>
       </c>
       <c r="H12" t="b">
         <v>0</v>
@@ -789,16 +789,16 @@
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5452</v>
+        <v>0.0852</v>
       </c>
       <c r="E13" t="n">
         <v>0.9</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.7498</v>
+        <v>-1.0445</v>
       </c>
       <c r="G13" t="n">
-        <v>2.8401</v>
+        <v>1.215</v>
       </c>
       <c r="H13" t="b">
         <v>0</v>
@@ -815,16 +815,16 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0319</v>
+        <v>-0.0466</v>
       </c>
       <c r="E14" t="n">
         <v>0.9</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.3682</v>
+        <v>-1.2281</v>
       </c>
       <c r="G14" t="n">
-        <v>2.432</v>
+        <v>1.1349</v>
       </c>
       <c r="H14" t="b">
         <v>0</v>
@@ -841,16 +841,16 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1514</v>
+        <v>0.111</v>
       </c>
       <c r="E15" t="n">
         <v>0.9</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.9761</v>
+        <v>-0.9362</v>
       </c>
       <c r="G15" t="n">
-        <v>2.2789</v>
+        <v>1.1583</v>
       </c>
       <c r="H15" t="b">
         <v>0</v>
@@ -867,16 +867,16 @@
         <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5629</v>
+        <v>0.4219</v>
       </c>
       <c r="E16" t="n">
         <v>0.9</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.7321</v>
+        <v>-0.7078</v>
       </c>
       <c r="G16" t="n">
-        <v>2.8578</v>
+        <v>1.5516</v>
       </c>
       <c r="H16" t="b">
         <v>0</v>
@@ -893,16 +893,16 @@
         <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>1.1425</v>
+        <v>0.167</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6898</v>
+        <v>0.9</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.0796</v>
+        <v>-0.9268</v>
       </c>
       <c r="G17" t="n">
-        <v>3.3646</v>
+        <v>1.2609</v>
       </c>
       <c r="H17" t="b">
         <v>0</v>
@@ -919,16 +919,16 @@
         <v>8</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2336</v>
+        <v>-0.1355</v>
       </c>
       <c r="E18" t="n">
         <v>0.9</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.9349</v>
+        <v>-1.203</v>
       </c>
       <c r="G18" t="n">
-        <v>2.4022</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="H18" t="b">
         <v>0</v>
@@ -945,16 +945,16 @@
         <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5133</v>
+        <v>-0.1319</v>
       </c>
       <c r="E19" t="n">
         <v>0.9</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.6213</v>
+        <v>-1.1696</v>
       </c>
       <c r="G19" t="n">
-        <v>1.5948</v>
+        <v>0.9059</v>
       </c>
       <c r="H19" t="b">
         <v>0</v>
@@ -971,16 +971,16 @@
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3937</v>
+        <v>0.0258</v>
       </c>
       <c r="E20" t="n">
         <v>0.9</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.1852</v>
+        <v>-0.8561</v>
       </c>
       <c r="G20" t="n">
-        <v>1.3978</v>
+        <v>0.9077</v>
       </c>
       <c r="H20" t="b">
         <v>0</v>
@@ -997,16 +997,16 @@
         <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0177</v>
+        <v>0.3367</v>
       </c>
       <c r="E21" t="n">
         <v>0.9</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.9698</v>
+        <v>-0.6417</v>
       </c>
       <c r="G21" t="n">
-        <v>2.0052</v>
+        <v>1.315</v>
       </c>
       <c r="H21" t="b">
         <v>0</v>
@@ -1023,16 +1023,16 @@
         <v>7</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5974</v>
+        <v>0.0818</v>
       </c>
       <c r="E22" t="n">
         <v>0.9</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.3055</v>
+        <v>-0.8549</v>
       </c>
       <c r="G22" t="n">
-        <v>2.5002</v>
+        <v>1.0185</v>
       </c>
       <c r="H22" t="b">
         <v>0</v>
@@ -1049,16 +1049,16 @@
         <v>8</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3115</v>
+        <v>-0.2207</v>
       </c>
       <c r="E23" t="n">
         <v>0.9</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.1516</v>
+        <v>-1.1265</v>
       </c>
       <c r="G23" t="n">
-        <v>1.5285</v>
+        <v>0.6851</v>
       </c>
       <c r="H23" t="b">
         <v>0</v>
@@ -1075,16 +1075,16 @@
         <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1195</v>
+        <v>0.1577</v>
       </c>
       <c r="E24" t="n">
         <v>0.9</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.8048</v>
+        <v>-0.7896</v>
       </c>
       <c r="G24" t="n">
-        <v>2.0439</v>
+        <v>1.105</v>
       </c>
       <c r="H24" t="b">
         <v>0</v>
@@ -1101,16 +1101,16 @@
         <v>6</v>
       </c>
       <c r="D25" t="n">
-        <v>0.531</v>
+        <v>0.4685</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9</v>
+        <v>0.8033</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.5771</v>
+        <v>-0.5692</v>
       </c>
       <c r="G25" t="n">
-        <v>2.639</v>
+        <v>1.5063</v>
       </c>
       <c r="H25" t="b">
         <v>0</v>
@@ -1127,16 +1127,16 @@
         <v>7</v>
       </c>
       <c r="D26" t="n">
-        <v>1.1106</v>
+        <v>0.2136</v>
       </c>
       <c r="E26" t="n">
-        <v>0.6294</v>
+        <v>0.9</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.9179</v>
+        <v>-0.7849</v>
       </c>
       <c r="G26" t="n">
-        <v>3.1391</v>
+        <v>1.2122</v>
       </c>
       <c r="H26" t="b">
         <v>0</v>
@@ -1153,16 +1153,16 @@
         <v>8</v>
       </c>
       <c r="D27" t="n">
-        <v>0.2017</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="E27" t="n">
         <v>0.9</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.7679</v>
+        <v>-1.0585</v>
       </c>
       <c r="G27" t="n">
-        <v>2.1714</v>
+        <v>0.8807</v>
       </c>
       <c r="H27" t="b">
         <v>0</v>
@@ -1179,16 +1179,16 @@
         <v>6</v>
       </c>
       <c r="D28" t="n">
-        <v>0.4114</v>
+        <v>0.3109</v>
       </c>
       <c r="E28" t="n">
         <v>0.9</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.3801</v>
+        <v>-0.571</v>
       </c>
       <c r="G28" t="n">
-        <v>2.2029</v>
+        <v>1.1928</v>
       </c>
       <c r="H28" t="b">
         <v>0</v>
@@ -1205,16 +1205,16 @@
         <v>7</v>
       </c>
       <c r="D29" t="n">
-        <v>0.9911</v>
+        <v>0.056</v>
       </c>
       <c r="E29" t="n">
-        <v>0.5633</v>
+        <v>0.9</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.7060999999999999</v>
+        <v>-0.7795</v>
       </c>
       <c r="G29" t="n">
-        <v>2.6882</v>
+        <v>0.8914</v>
       </c>
       <c r="H29" t="b">
         <v>0</v>
@@ -1231,16 +1231,16 @@
         <v>8</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0822</v>
+        <v>-0.2465</v>
       </c>
       <c r="E30" t="n">
         <v>0.9</v>
       </c>
       <c r="F30" t="n">
-        <v>-1.5442</v>
+        <v>-1.0472</v>
       </c>
       <c r="G30" t="n">
-        <v>1.7086</v>
+        <v>0.5541</v>
       </c>
       <c r="H30" t="b">
         <v>0</v>
@@ -1257,16 +1257,16 @@
         <v>7</v>
       </c>
       <c r="D31" t="n">
-        <v>0.5796</v>
+        <v>-0.2549</v>
       </c>
       <c r="E31" t="n">
         <v>0.9</v>
       </c>
       <c r="F31" t="n">
-        <v>-1.3232</v>
+        <v>-1.1916</v>
       </c>
       <c r="G31" t="n">
-        <v>2.4825</v>
+        <v>0.6818</v>
       </c>
       <c r="H31" t="b">
         <v>0</v>
@@ -1283,16 +1283,16 @@
         <v>8</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.3292</v>
+        <v>-0.5574</v>
       </c>
       <c r="E32" t="n">
-        <v>0.9</v>
+        <v>0.5064</v>
       </c>
       <c r="F32" t="n">
-        <v>-2.1693</v>
+        <v>-1.4632</v>
       </c>
       <c r="G32" t="n">
-        <v>1.5108</v>
+        <v>0.3484</v>
       </c>
       <c r="H32" t="b">
         <v>0</v>
@@ -1309,16 +1309,16 @@
         <v>8</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.9089</v>
+        <v>-0.3025</v>
       </c>
       <c r="E33" t="n">
-        <v>0.6795</v>
+        <v>0.9</v>
       </c>
       <c r="F33" t="n">
-        <v>-2.6572</v>
+        <v>-1.1632</v>
       </c>
       <c r="G33" t="n">
-        <v>0.8394</v>
+        <v>0.5581</v>
       </c>
       <c r="H33" t="b">
         <v>0</v>
@@ -1390,16 +1390,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.33</v>
+        <v>0.0588</v>
       </c>
       <c r="E2" t="n">
-        <v>0.307</v>
+        <v>0.7478</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.9775</v>
+        <v>-0.2956</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3176</v>
+        <v>0.4133</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
@@ -1420,16 +1420,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.1017</v>
+        <v>0.015</v>
       </c>
       <c r="E3" t="n">
         <v>0.9</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.4747</v>
+        <v>-0.722</v>
       </c>
       <c r="G3" t="n">
-        <v>1.2714</v>
+        <v>0.7521</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
@@ -1450,16 +1450,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.0728</v>
+        <v>-0.1178</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9</v>
+        <v>0.8835</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.0889</v>
+        <v>-0.7413999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>1.2346</v>
+        <v>0.5059</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
@@ -1480,16 +1480,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.1745</v>
+        <v>-0.1328</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9</v>
+        <v>0.8074</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.8431</v>
+        <v>-0.679</v>
       </c>
       <c r="G5" t="n">
-        <v>1.1921</v>
+        <v>0.4135</v>
       </c>
       <c r="H5" t="b">
         <v>0</v>
@@ -1510,16 +1510,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.4147</v>
+        <v>-0.1174</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1971</v>
+        <v>0.5029</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.0559</v>
+        <v>-0.47</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2265</v>
+        <v>0.2352</v>
       </c>
       <c r="H6" t="b">
         <v>0</v>
@@ -1540,16 +1540,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.3092</v>
+        <v>-0.2219</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3522</v>
+        <v>0.2132</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3578</v>
+        <v>-0.5777</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9761</v>
+        <v>0.134</v>
       </c>
       <c r="H7" t="b">
         <v>0</v>
@@ -1566,16 +1566,16 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.4503</v>
+        <v>-0.036</v>
       </c>
       <c r="E8" t="n">
-        <v>0.179</v>
+        <v>0.9</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.2418</v>
+        <v>-1.1247</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3412</v>
+        <v>1.0527</v>
       </c>
       <c r="H8" t="b">
         <v>0</v>
@@ -1592,16 +1592,16 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.6451</v>
+        <v>-0.2745</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1322</v>
+        <v>0.9</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.5625</v>
+        <v>-1.4397</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2723</v>
+        <v>0.8907</v>
       </c>
       <c r="H9" t="b">
         <v>0</v>
@@ -1618,16 +1618,16 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.6194</v>
+        <v>-0.1029</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1168</v>
+        <v>0.9</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.4644</v>
+        <v>-1.2241</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2256</v>
+        <v>1.0184</v>
       </c>
       <c r="H10" t="b">
         <v>0</v>
@@ -1644,16 +1644,16 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.5673</v>
+        <v>-0.2178</v>
       </c>
       <c r="E11" t="n">
-        <v>0.453</v>
+        <v>0.9</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.0426</v>
+        <v>-1.7221</v>
       </c>
       <c r="G11" t="n">
-        <v>0.908</v>
+        <v>1.2865</v>
       </c>
       <c r="H11" t="b">
         <v>0</v>
@@ -1670,16 +1670,16 @@
         <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.4052</v>
+        <v>0.1304</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2778</v>
+        <v>0.9</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.3225</v>
+        <v>-1.0349</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5122</v>
+        <v>1.2956</v>
       </c>
       <c r="H12" t="b">
         <v>0</v>
@@ -1696,16 +1696,16 @@
         <v>7</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.6824</v>
+        <v>-0.3588</v>
       </c>
       <c r="E13" t="n">
-        <v>0.3654</v>
+        <v>0.9</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.1577</v>
+        <v>-1.8631</v>
       </c>
       <c r="G13" t="n">
-        <v>0.793</v>
+        <v>1.1455</v>
       </c>
       <c r="H13" t="b">
         <v>0</v>
@@ -1722,16 +1722,16 @@
         <v>8</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.1281</v>
+        <v>0.2657</v>
       </c>
       <c r="E14" t="n">
-        <v>0.6655</v>
+        <v>0.9</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.3112</v>
+        <v>-1.061</v>
       </c>
       <c r="G14" t="n">
-        <v>1.0549</v>
+        <v>1.5923</v>
       </c>
       <c r="H14" t="b">
         <v>0</v>
@@ -1748,16 +1748,16 @@
         <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1948</v>
+        <v>-0.2385</v>
       </c>
       <c r="E15" t="n">
         <v>0.9</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.8684</v>
+        <v>-1.2556</v>
       </c>
       <c r="G15" t="n">
-        <v>1.4788</v>
+        <v>0.7786</v>
       </c>
       <c r="H15" t="b">
         <v>0</v>
@@ -1774,16 +1774,16 @@
         <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1691</v>
+        <v>-0.0669</v>
       </c>
       <c r="E16" t="n">
         <v>0.9</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.7592</v>
+        <v>-1.0332</v>
       </c>
       <c r="G16" t="n">
-        <v>1.4211</v>
+        <v>0.8995</v>
       </c>
       <c r="H16" t="b">
         <v>0</v>
@@ -1800,16 +1800,16 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.117</v>
+        <v>-0.1818</v>
       </c>
       <c r="E17" t="n">
         <v>0.9</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.4087</v>
+        <v>-1.5745</v>
       </c>
       <c r="G17" t="n">
-        <v>2.1747</v>
+        <v>1.2109</v>
       </c>
       <c r="H17" t="b">
         <v>0</v>
@@ -1826,16 +1826,16 @@
         <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0451</v>
+        <v>0.1664</v>
       </c>
       <c r="E18" t="n">
         <v>0.9</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.6285</v>
+        <v>-0.8507</v>
       </c>
       <c r="G18" t="n">
-        <v>1.7188</v>
+        <v>1.1834</v>
       </c>
       <c r="H18" t="b">
         <v>0</v>
@@ -1852,16 +1852,16 @@
         <v>7</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.232</v>
+        <v>-0.3228</v>
       </c>
       <c r="E19" t="n">
         <v>0.9</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.5237</v>
+        <v>-1.7155</v>
       </c>
       <c r="G19" t="n">
-        <v>2.0596</v>
+        <v>1.0699</v>
       </c>
       <c r="H19" t="b">
         <v>0</v>
@@ -1878,16 +1878,16 @@
         <v>8</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3222</v>
+        <v>0.3017</v>
       </c>
       <c r="E20" t="n">
         <v>0.9</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.6502</v>
+        <v>-0.897</v>
       </c>
       <c r="G20" t="n">
-        <v>2.2945</v>
+        <v>1.5003</v>
       </c>
       <c r="H20" t="b">
         <v>0</v>
@@ -1904,16 +1904,16 @@
         <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0257</v>
+        <v>0.1716</v>
       </c>
       <c r="E21" t="n">
         <v>0.9</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.705</v>
+        <v>-0.8802</v>
       </c>
       <c r="G21" t="n">
-        <v>1.7565</v>
+        <v>1.2234</v>
       </c>
       <c r="H21" t="b">
         <v>0</v>
@@ -1930,16 +1930,16 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>0.07779999999999999</v>
+        <v>0.0567</v>
       </c>
       <c r="E22" t="n">
         <v>0.9</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.3136</v>
+        <v>-1.3966</v>
       </c>
       <c r="G22" t="n">
-        <v>2.4692</v>
+        <v>1.51</v>
       </c>
       <c r="H22" t="b">
         <v>0</v>
@@ -1956,16 +1956,16 @@
         <v>6</v>
       </c>
       <c r="D23" t="n">
-        <v>0.2399</v>
+        <v>0.4048</v>
       </c>
       <c r="E23" t="n">
         <v>0.9</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.5678</v>
+        <v>-0.6937</v>
       </c>
       <c r="G23" t="n">
-        <v>2.0476</v>
+        <v>1.5034</v>
       </c>
       <c r="H23" t="b">
         <v>0</v>
@@ -1982,16 +1982,16 @@
         <v>7</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.0373</v>
+        <v>-0.0844</v>
       </c>
       <c r="E24" t="n">
         <v>0.9</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.4286</v>
+        <v>-1.5376</v>
       </c>
       <c r="G24" t="n">
-        <v>2.3541</v>
+        <v>1.3689</v>
       </c>
       <c r="H24" t="b">
         <v>0</v>
@@ -2008,16 +2008,16 @@
         <v>8</v>
       </c>
       <c r="D25" t="n">
-        <v>0.517</v>
+        <v>0.5402</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9</v>
+        <v>0.8304</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.5704</v>
+        <v>-0.7284</v>
       </c>
       <c r="G25" t="n">
-        <v>2.6043</v>
+        <v>1.8087</v>
       </c>
       <c r="H25" t="b">
         <v>0</v>
@@ -2034,16 +2034,16 @@
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0521</v>
+        <v>-0.1149</v>
       </c>
       <c r="E26" t="n">
         <v>0.9</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.2817</v>
+        <v>-1.5332</v>
       </c>
       <c r="G26" t="n">
-        <v>2.3858</v>
+        <v>1.3033</v>
       </c>
       <c r="H26" t="b">
         <v>0</v>
@@ -2060,16 +2060,16 @@
         <v>6</v>
       </c>
       <c r="D27" t="n">
-        <v>0.2142</v>
+        <v>0.2332</v>
       </c>
       <c r="E27" t="n">
         <v>0.9</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.5165</v>
+        <v>-0.8186</v>
       </c>
       <c r="G27" t="n">
-        <v>1.945</v>
+        <v>1.285</v>
       </c>
       <c r="H27" t="b">
         <v>0</v>
@@ -2086,16 +2086,16 @@
         <v>7</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.063</v>
+        <v>-0.256</v>
       </c>
       <c r="E28" t="n">
         <v>0.9</v>
       </c>
       <c r="F28" t="n">
-        <v>-2.3967</v>
+        <v>-1.6742</v>
       </c>
       <c r="G28" t="n">
-        <v>2.2708</v>
+        <v>1.1623</v>
       </c>
       <c r="H28" t="b">
         <v>0</v>
@@ -2112,16 +2112,16 @@
         <v>8</v>
       </c>
       <c r="D29" t="n">
-        <v>0.4912</v>
+        <v>0.3685</v>
       </c>
       <c r="E29" t="n">
         <v>0.9</v>
       </c>
       <c r="F29" t="n">
-        <v>-1.5298</v>
+        <v>-0.8597</v>
       </c>
       <c r="G29" t="n">
-        <v>2.5123</v>
+        <v>1.5968</v>
       </c>
       <c r="H29" t="b">
         <v>0</v>
@@ -2138,16 +2138,16 @@
         <v>6</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1621</v>
+        <v>0.3481</v>
       </c>
       <c r="E30" t="n">
         <v>0.9</v>
       </c>
       <c r="F30" t="n">
-        <v>-2.2292</v>
+        <v>-1.1051</v>
       </c>
       <c r="G30" t="n">
-        <v>2.5535</v>
+        <v>1.8014</v>
       </c>
       <c r="H30" t="b">
         <v>0</v>
@@ -2164,16 +2164,16 @@
         <v>7</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.1151</v>
+        <v>-0.141</v>
       </c>
       <c r="E31" t="n">
         <v>0.9</v>
       </c>
       <c r="F31" t="n">
-        <v>-2.9733</v>
+        <v>-1.878</v>
       </c>
       <c r="G31" t="n">
-        <v>2.7432</v>
+        <v>1.5959</v>
       </c>
       <c r="H31" t="b">
         <v>0</v>
@@ -2190,16 +2190,16 @@
         <v>8</v>
       </c>
       <c r="D32" t="n">
-        <v>0.4392</v>
+        <v>0.4835</v>
       </c>
       <c r="E32" t="n">
         <v>0.9</v>
       </c>
       <c r="F32" t="n">
-        <v>-2.17</v>
+        <v>-1.1022</v>
       </c>
       <c r="G32" t="n">
-        <v>3.0484</v>
+        <v>2.0691</v>
       </c>
       <c r="H32" t="b">
         <v>0</v>
@@ -2216,16 +2216,16 @@
         <v>7</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.2772</v>
+        <v>-0.4892</v>
       </c>
       <c r="E33" t="n">
         <v>0.9</v>
       </c>
       <c r="F33" t="n">
-        <v>-2.6686</v>
+        <v>-1.9425</v>
       </c>
       <c r="G33" t="n">
-        <v>2.1142</v>
+        <v>0.9641</v>
       </c>
       <c r="H33" t="b">
         <v>0</v>
@@ -2242,16 +2242,16 @@
         <v>8</v>
       </c>
       <c r="D34" t="n">
-        <v>0.277</v>
+        <v>0.1353</v>
       </c>
       <c r="E34" t="n">
         <v>0.9</v>
       </c>
       <c r="F34" t="n">
-        <v>-1.8103</v>
+        <v>-1.1332</v>
       </c>
       <c r="G34" t="n">
-        <v>2.3644</v>
+        <v>1.4039</v>
       </c>
       <c r="H34" t="b">
         <v>0</v>
@@ -2268,16 +2268,16 @@
         <v>8</v>
       </c>
       <c r="D35" t="n">
-        <v>0.5542</v>
+        <v>0.6245000000000001</v>
       </c>
       <c r="E35" t="n">
-        <v>0.9</v>
+        <v>0.8883</v>
       </c>
       <c r="F35" t="n">
-        <v>-2.055</v>
+        <v>-0.9611</v>
       </c>
       <c r="G35" t="n">
-        <v>3.1634</v>
+        <v>2.2102</v>
       </c>
       <c r="H35" t="b">
         <v>0</v>
@@ -2349,16 +2349,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-2.2217</v>
+        <v>0.4349</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2873</v>
+        <v>0.6894</v>
       </c>
       <c r="F2" t="n">
-        <v>-6.404</v>
+        <v>-1.6784</v>
       </c>
       <c r="G2" t="n">
-        <v>1.9605</v>
+        <v>2.5482</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
@@ -2379,16 +2379,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-1.5608</v>
+        <v>-0.5729</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8995</v>
+        <v>0.9</v>
       </c>
       <c r="F3" t="n">
-        <v>-10.3601</v>
+        <v>-4.9981</v>
       </c>
       <c r="G3" t="n">
-        <v>7.2385</v>
+        <v>3.8523</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
@@ -2409,16 +2409,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.7413</v>
+        <v>-0.3407</v>
       </c>
       <c r="E4" t="n">
         <v>0.9</v>
       </c>
       <c r="F4" t="n">
-        <v>-6.7039</v>
+        <v>-4.0849</v>
       </c>
       <c r="G4" t="n">
-        <v>8.186500000000001</v>
+        <v>3.4035</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
@@ -2439,16 +2439,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2.3021</v>
+        <v>0.2322</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6532</v>
+        <v>0.9</v>
       </c>
       <c r="F5" t="n">
-        <v>-4.2191</v>
+        <v>-3.0473</v>
       </c>
       <c r="G5" t="n">
-        <v>8.8233</v>
+        <v>3.5118</v>
       </c>
       <c r="H5" t="b">
         <v>0</v>
@@ -2469,16 +2469,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-2.254</v>
+        <v>-0.9103</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2802</v>
+        <v>0.3824</v>
       </c>
       <c r="F6" t="n">
-        <v>-6.434</v>
+        <v>-3.0039</v>
       </c>
       <c r="G6" t="n">
-        <v>1.926</v>
+        <v>1.1834</v>
       </c>
       <c r="H6" t="b">
         <v>0</v>
@@ -2499,16 +2499,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.1266</v>
+        <v>-1.8023</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6118</v>
+        <v>0.0868</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.228</v>
+        <v>-3.8799</v>
       </c>
       <c r="G7" t="n">
-        <v>5.4812</v>
+        <v>0.2753</v>
       </c>
       <c r="H7" t="b">
         <v>0</v>
@@ -2525,16 +2525,16 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>-6.87</v>
+        <v>1.4871</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5731000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="F8" t="n">
-        <v>-18.9688</v>
+        <v>-4.8233</v>
       </c>
       <c r="G8" t="n">
-        <v>5.2288</v>
+        <v>7.7976</v>
       </c>
       <c r="H8" t="b">
         <v>0</v>
@@ -2551,16 +2551,16 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>-9.045299999999999</v>
+        <v>-1.3038</v>
       </c>
       <c r="E9" t="n">
-        <v>0.332</v>
+        <v>0.9</v>
       </c>
       <c r="F9" t="n">
-        <v>-21.9941</v>
+        <v>-8.057700000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>3.9036</v>
+        <v>5.45</v>
       </c>
       <c r="H9" t="b">
         <v>0</v>
@@ -2577,16 +2577,16 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>-8.715299999999999</v>
+        <v>-0.3043</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3304</v>
+        <v>0.9</v>
       </c>
       <c r="F10" t="n">
-        <v>-21.1753</v>
+        <v>-6.8031</v>
       </c>
       <c r="G10" t="n">
-        <v>3.7447</v>
+        <v>6.1946</v>
       </c>
       <c r="H10" t="b">
         <v>0</v>
@@ -2603,16 +2603,16 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>-9.375999999999999</v>
+        <v>-1.2876</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5857</v>
+        <v>0.9</v>
       </c>
       <c r="F11" t="n">
-        <v>-26.0928</v>
+        <v>-10.0067</v>
       </c>
       <c r="G11" t="n">
-        <v>7.3409</v>
+        <v>7.4316</v>
       </c>
       <c r="H11" t="b">
         <v>0</v>
@@ -2629,16 +2629,16 @@
         <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.7386</v>
+        <v>0.3213</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3742</v>
+        <v>0.9</v>
       </c>
       <c r="F12" t="n">
-        <v>-21.6874</v>
+        <v>-6.4325</v>
       </c>
       <c r="G12" t="n">
-        <v>4.2103</v>
+        <v>7.0752</v>
       </c>
       <c r="H12" t="b">
         <v>0</v>
@@ -2655,16 +2655,16 @@
         <v>7</v>
       </c>
       <c r="D13" t="n">
-        <v>-10.298</v>
+        <v>-2.0635</v>
       </c>
       <c r="E13" t="n">
-        <v>0.4854</v>
+        <v>0.9</v>
       </c>
       <c r="F13" t="n">
-        <v>-27.0149</v>
+        <v>-10.7827</v>
       </c>
       <c r="G13" t="n">
-        <v>6.4189</v>
+        <v>6.6556</v>
       </c>
       <c r="H13" t="b">
         <v>0</v>
@@ -2681,16 +2681,16 @@
         <v>8</v>
       </c>
       <c r="D14" t="n">
-        <v>-5.4011</v>
+        <v>2.1</v>
       </c>
       <c r="E14" t="n">
         <v>0.9</v>
       </c>
       <c r="F14" t="n">
-        <v>-20.144</v>
+        <v>-5.5896</v>
       </c>
       <c r="G14" t="n">
-        <v>9.341799999999999</v>
+        <v>9.7895</v>
       </c>
       <c r="H14" t="b">
         <v>0</v>
@@ -2707,16 +2707,16 @@
         <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>-2.1753</v>
+        <v>-2.7909</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9</v>
+        <v>0.7441</v>
       </c>
       <c r="F15" t="n">
-        <v>-13.4779</v>
+        <v>-8.686199999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>9.1274</v>
+        <v>3.1043</v>
       </c>
       <c r="H15" t="b">
         <v>0</v>
@@ -2733,16 +2733,16 @@
         <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.8453</v>
+        <v>-1.7914</v>
       </c>
       <c r="E16" t="n">
         <v>0.9</v>
       </c>
       <c r="F16" t="n">
-        <v>-12.5845</v>
+        <v>-7.3927</v>
       </c>
       <c r="G16" t="n">
-        <v>8.8939</v>
+        <v>3.81</v>
       </c>
       <c r="H16" t="b">
         <v>0</v>
@@ -2759,16 +2759,16 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.5059</v>
+        <v>-2.7747</v>
       </c>
       <c r="E17" t="n">
         <v>0.9</v>
       </c>
       <c r="F17" t="n">
-        <v>-17.9828</v>
+        <v>-10.847</v>
       </c>
       <c r="G17" t="n">
-        <v>12.9709</v>
+        <v>5.2977</v>
       </c>
       <c r="H17" t="b">
         <v>0</v>
@@ -2785,16 +2785,16 @@
         <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.8685</v>
+        <v>-1.1658</v>
       </c>
       <c r="E18" t="n">
         <v>0.9</v>
       </c>
       <c r="F18" t="n">
-        <v>-13.1712</v>
+        <v>-7.061</v>
       </c>
       <c r="G18" t="n">
-        <v>9.434100000000001</v>
+        <v>4.7294</v>
       </c>
       <c r="H18" t="b">
         <v>0</v>
@@ -2811,16 +2811,16 @@
         <v>7</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.428</v>
+        <v>-3.5506</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9</v>
+        <v>0.8048999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>-18.9048</v>
+        <v>-11.623</v>
       </c>
       <c r="G19" t="n">
-        <v>12.0488</v>
+        <v>4.5217</v>
       </c>
       <c r="H19" t="b">
         <v>0</v>
@@ -2837,16 +2837,16 @@
         <v>8</v>
       </c>
       <c r="D20" t="n">
-        <v>1.4689</v>
+        <v>0.6129</v>
       </c>
       <c r="E20" t="n">
         <v>0.9</v>
       </c>
       <c r="F20" t="n">
-        <v>-11.8514</v>
+        <v>-6.3347</v>
       </c>
       <c r="G20" t="n">
-        <v>14.7893</v>
+        <v>7.5604</v>
       </c>
       <c r="H20" t="b">
         <v>0</v>
@@ -2863,16 +2863,16 @@
         <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>0.33</v>
+        <v>0.9996</v>
       </c>
       <c r="E21" t="n">
         <v>0.9</v>
       </c>
       <c r="F21" t="n">
-        <v>-11.3586</v>
+        <v>-5.0969</v>
       </c>
       <c r="G21" t="n">
-        <v>12.0185</v>
+        <v>7.0961</v>
       </c>
       <c r="H21" t="b">
         <v>0</v>
@@ -2889,16 +2889,16 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3307</v>
+        <v>0.0163</v>
       </c>
       <c r="E22" t="n">
         <v>0.9</v>
       </c>
       <c r="F22" t="n">
-        <v>-16.4807</v>
+        <v>-8.4072</v>
       </c>
       <c r="G22" t="n">
-        <v>15.8194</v>
+        <v>8.4398</v>
       </c>
       <c r="H22" t="b">
         <v>0</v>
@@ -2915,16 +2915,16 @@
         <v>6</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3067</v>
+        <v>1.6252</v>
       </c>
       <c r="E23" t="n">
         <v>0.9</v>
       </c>
       <c r="F23" t="n">
-        <v>-11.9016</v>
+        <v>-4.7424</v>
       </c>
       <c r="G23" t="n">
-        <v>12.515</v>
+        <v>7.9927</v>
       </c>
       <c r="H23" t="b">
         <v>0</v>
@@ -2941,16 +2941,16 @@
         <v>7</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.2527</v>
+        <v>-0.7597</v>
       </c>
       <c r="E24" t="n">
         <v>0.9</v>
       </c>
       <c r="F24" t="n">
-        <v>-17.4028</v>
+        <v>-9.183199999999999</v>
       </c>
       <c r="G24" t="n">
-        <v>14.8973</v>
+        <v>7.6638</v>
       </c>
       <c r="H24" t="b">
         <v>0</v>
@@ -2967,16 +2967,16 @@
         <v>8</v>
       </c>
       <c r="D25" t="n">
-        <v>3.6442</v>
+        <v>3.4038</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9</v>
+        <v>0.7631</v>
       </c>
       <c r="F25" t="n">
-        <v>-10.4527</v>
+        <v>-3.9488</v>
       </c>
       <c r="G25" t="n">
-        <v>17.7411</v>
+        <v>10.7564</v>
       </c>
       <c r="H25" t="b">
         <v>0</v>
@@ -2993,16 +2993,16 @@
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.6607</v>
+        <v>-0.9833</v>
       </c>
       <c r="E26" t="n">
         <v>0.9</v>
       </c>
       <c r="F26" t="n">
-        <v>-16.4215</v>
+        <v>-9.203799999999999</v>
       </c>
       <c r="G26" t="n">
-        <v>15.1002</v>
+        <v>7.2372</v>
       </c>
       <c r="H26" t="b">
         <v>0</v>
@@ -3019,16 +3019,16 @@
         <v>6</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.0233</v>
+        <v>0.6256</v>
       </c>
       <c r="E27" t="n">
         <v>0.9</v>
       </c>
       <c r="F27" t="n">
-        <v>-11.7118</v>
+        <v>-5.4709</v>
       </c>
       <c r="G27" t="n">
-        <v>11.6653</v>
+        <v>6.7221</v>
       </c>
       <c r="H27" t="b">
         <v>0</v>
@@ -3045,16 +3045,16 @@
         <v>7</v>
       </c>
       <c r="D28" t="n">
-        <v>-1.5827</v>
+        <v>-1.7593</v>
       </c>
       <c r="E28" t="n">
         <v>0.9</v>
       </c>
       <c r="F28" t="n">
-        <v>-17.3436</v>
+        <v>-9.979799999999999</v>
       </c>
       <c r="G28" t="n">
-        <v>14.1781</v>
+        <v>6.4612</v>
       </c>
       <c r="H28" t="b">
         <v>0</v>
@@ -3071,16 +3071,16 @@
         <v>8</v>
       </c>
       <c r="D29" t="n">
-        <v>3.3142</v>
+        <v>2.4042</v>
       </c>
       <c r="E29" t="n">
         <v>0.9</v>
       </c>
       <c r="F29" t="n">
-        <v>-10.3351</v>
+        <v>-4.7149</v>
       </c>
       <c r="G29" t="n">
-        <v>16.9635</v>
+        <v>9.523400000000001</v>
       </c>
       <c r="H29" t="b">
         <v>0</v>
@@ -3097,16 +3097,16 @@
         <v>6</v>
       </c>
       <c r="D30" t="n">
-        <v>0.6374</v>
+        <v>1.6089</v>
       </c>
       <c r="E30" t="n">
         <v>0.9</v>
       </c>
       <c r="F30" t="n">
-        <v>-15.5127</v>
+        <v>-6.8146</v>
       </c>
       <c r="G30" t="n">
-        <v>16.7874</v>
+        <v>10.0324</v>
       </c>
       <c r="H30" t="b">
         <v>0</v>
@@ -3123,16 +3123,16 @@
         <v>7</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.9221</v>
+        <v>-0.7759</v>
       </c>
       <c r="E31" t="n">
         <v>0.9</v>
       </c>
       <c r="F31" t="n">
-        <v>-20.2251</v>
+        <v>-10.8439</v>
       </c>
       <c r="G31" t="n">
-        <v>18.3809</v>
+        <v>9.2921</v>
       </c>
       <c r="H31" t="b">
         <v>0</v>
@@ -3149,16 +3149,16 @@
         <v>8</v>
       </c>
       <c r="D32" t="n">
-        <v>3.9749</v>
+        <v>3.3875</v>
       </c>
       <c r="E32" t="n">
         <v>0.9</v>
       </c>
       <c r="F32" t="n">
-        <v>-13.6463</v>
+        <v>-5.8033</v>
       </c>
       <c r="G32" t="n">
-        <v>21.596</v>
+        <v>12.5783</v>
       </c>
       <c r="H32" t="b">
         <v>0</v>
@@ -3175,16 +3175,16 @@
         <v>7</v>
       </c>
       <c r="D33" t="n">
-        <v>-1.5595</v>
+        <v>-2.3848</v>
       </c>
       <c r="E33" t="n">
         <v>0.9</v>
       </c>
       <c r="F33" t="n">
-        <v>-17.7095</v>
+        <v>-10.8083</v>
       </c>
       <c r="G33" t="n">
-        <v>14.5906</v>
+        <v>6.0387</v>
       </c>
       <c r="H33" t="b">
         <v>0</v>
@@ -3201,16 +3201,16 @@
         <v>8</v>
       </c>
       <c r="D34" t="n">
-        <v>3.3375</v>
+        <v>1.7786</v>
       </c>
       <c r="E34" t="n">
         <v>0.9</v>
       </c>
       <c r="F34" t="n">
-        <v>-10.7594</v>
+        <v>-5.574</v>
       </c>
       <c r="G34" t="n">
-        <v>17.4344</v>
+        <v>9.1313</v>
       </c>
       <c r="H34" t="b">
         <v>0</v>
@@ -3227,16 +3227,16 @@
         <v>8</v>
       </c>
       <c r="D35" t="n">
-        <v>4.8969</v>
+        <v>4.1635</v>
       </c>
       <c r="E35" t="n">
-        <v>0.9</v>
+        <v>0.7811</v>
       </c>
       <c r="F35" t="n">
-        <v>-12.7242</v>
+        <v>-5.0273</v>
       </c>
       <c r="G35" t="n">
-        <v>22.5181</v>
+        <v>13.3543</v>
       </c>
       <c r="H35" t="b">
         <v>0</v>
@@ -3308,16 +3308,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.6458</v>
+        <v>14.6488</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8619</v>
+        <v>0.1155</v>
       </c>
       <c r="F2" t="n">
-        <v>-17.0273</v>
+        <v>-3.7947</v>
       </c>
       <c r="G2" t="n">
-        <v>20.3188</v>
+        <v>33.0923</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
@@ -3338,16 +3338,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-5.9621</v>
+        <v>-3.7234</v>
       </c>
       <c r="E3" t="n">
         <v>0.9</v>
       </c>
       <c r="F3" t="n">
-        <v>-44.9461</v>
+        <v>-43.8118</v>
       </c>
       <c r="G3" t="n">
-        <v>33.022</v>
+        <v>36.3649</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
@@ -3368,16 +3368,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-2.7184</v>
+        <v>-2.6672</v>
       </c>
       <c r="E4" t="n">
         <v>0.9</v>
       </c>
       <c r="F4" t="n">
-        <v>-35.7034</v>
+        <v>-36.5865</v>
       </c>
       <c r="G4" t="n">
-        <v>30.2665</v>
+        <v>31.2521</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
@@ -3398,16 +3398,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3.2436</v>
+        <v>1.0563</v>
       </c>
       <c r="E5" t="n">
         <v>0.9</v>
       </c>
       <c r="F5" t="n">
-        <v>-25.6478</v>
+        <v>-28.6536</v>
       </c>
       <c r="G5" t="n">
-        <v>32.1351</v>
+        <v>30.7661</v>
       </c>
       <c r="H5" t="b">
         <v>0</v>
@@ -3428,16 +3428,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>9.3734</v>
+        <v>-1.2709</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3066</v>
+        <v>0.894</v>
       </c>
       <c r="F6" t="n">
-        <v>-9.0016</v>
+        <v>-20.4484</v>
       </c>
       <c r="G6" t="n">
-        <v>27.7484</v>
+        <v>17.9066</v>
       </c>
       <c r="H6" t="b">
         <v>0</v>
@@ -3458,16 +3458,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>4.0999</v>
+        <v>-1.7818</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6768999999999999</v>
+        <v>0.8585</v>
       </c>
       <c r="F7" t="n">
-        <v>-15.0321</v>
+        <v>-21.4743</v>
       </c>
       <c r="G7" t="n">
-        <v>23.2318</v>
+        <v>17.9106</v>
       </c>
       <c r="H7" t="b">
         <v>0</v>
@@ -3484,16 +3484,16 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>27.6225</v>
+        <v>34.5237</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6332</v>
+        <v>0.423</v>
       </c>
       <c r="F8" t="n">
-        <v>-24.0457</v>
+        <v>-18.6813</v>
       </c>
       <c r="G8" t="n">
-        <v>79.2907</v>
+        <v>87.7287</v>
       </c>
       <c r="H8" t="b">
         <v>0</v>
@@ -3510,16 +3510,16 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>40.2</v>
+        <v>26.7983</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2867</v>
+        <v>0.7492</v>
       </c>
       <c r="F9" t="n">
-        <v>-15.0984</v>
+        <v>-30.1448</v>
       </c>
       <c r="G9" t="n">
-        <v>95.4983</v>
+        <v>83.7414</v>
       </c>
       <c r="H9" t="b">
         <v>0</v>
@@ -3536,16 +3536,16 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>19.2322</v>
+        <v>10.8441</v>
       </c>
       <c r="E10" t="n">
         <v>0.9</v>
       </c>
       <c r="F10" t="n">
-        <v>-33.9787</v>
+        <v>-43.9495</v>
       </c>
       <c r="G10" t="n">
-        <v>72.443</v>
+        <v>65.63760000000001</v>
       </c>
       <c r="H10" t="b">
         <v>0</v>
@@ -3562,16 +3562,16 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>12.2642</v>
+        <v>7.2</v>
       </c>
       <c r="E11" t="n">
         <v>0.9</v>
       </c>
       <c r="F11" t="n">
-        <v>-59.1257</v>
+        <v>-66.3133</v>
       </c>
       <c r="G11" t="n">
-        <v>83.6541</v>
+        <v>80.7133</v>
       </c>
       <c r="H11" t="b">
         <v>0</v>
@@ -3588,16 +3588,16 @@
         <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>22.9919</v>
+        <v>23.6872</v>
       </c>
       <c r="E12" t="n">
-        <v>0.8485</v>
+        <v>0.8482</v>
       </c>
       <c r="F12" t="n">
-        <v>-32.3065</v>
+        <v>-33.2559</v>
       </c>
       <c r="G12" t="n">
-        <v>78.2903</v>
+        <v>80.63030000000001</v>
       </c>
       <c r="H12" t="b">
         <v>0</v>
@@ -3614,16 +3614,16 @@
         <v>7</v>
       </c>
       <c r="D13" t="n">
-        <v>52.5614</v>
+        <v>50</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2727</v>
+        <v>0.3645</v>
       </c>
       <c r="F13" t="n">
-        <v>-18.8284</v>
+        <v>-23.5133</v>
       </c>
       <c r="G13" t="n">
-        <v>123.9513</v>
+        <v>123.5133</v>
       </c>
       <c r="H13" t="b">
         <v>0</v>
@@ -3640,16 +3640,16 @@
         <v>8</v>
       </c>
       <c r="D14" t="n">
-        <v>8.107200000000001</v>
+        <v>4.5</v>
       </c>
       <c r="E14" t="n">
         <v>0.9</v>
       </c>
       <c r="F14" t="n">
-        <v>-54.8527</v>
+        <v>-60.3326</v>
       </c>
       <c r="G14" t="n">
-        <v>71.0672</v>
+        <v>69.3326</v>
       </c>
       <c r="H14" t="b">
         <v>0</v>
@@ -3666,16 +3666,16 @@
         <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>12.5775</v>
+        <v>-7.7254</v>
       </c>
       <c r="E15" t="n">
         <v>0.9</v>
       </c>
       <c r="F15" t="n">
-        <v>-35.6909</v>
+        <v>-57.4294</v>
       </c>
       <c r="G15" t="n">
-        <v>60.8458</v>
+        <v>41.9786</v>
       </c>
       <c r="H15" t="b">
         <v>0</v>
@@ -3692,16 +3692,16 @@
         <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>-8.3904</v>
+        <v>-23.6796</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9</v>
+        <v>0.6934</v>
       </c>
       <c r="F16" t="n">
-        <v>-54.2524</v>
+        <v>-70.9057</v>
       </c>
       <c r="G16" t="n">
-        <v>37.4716</v>
+        <v>23.5465</v>
       </c>
       <c r="H16" t="b">
         <v>0</v>
@@ -3718,16 +3718,16 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>-15.3583</v>
+        <v>-27.3237</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9</v>
+        <v>0.8745000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>-81.4525</v>
+        <v>-95.3837</v>
       </c>
       <c r="G17" t="n">
-        <v>50.7359</v>
+        <v>40.7364</v>
       </c>
       <c r="H17" t="b">
         <v>0</v>
@@ -3744,16 +3744,16 @@
         <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>-4.6306</v>
+        <v>-10.8365</v>
       </c>
       <c r="E18" t="n">
         <v>0.9</v>
       </c>
       <c r="F18" t="n">
-        <v>-52.899</v>
+        <v>-60.5405</v>
       </c>
       <c r="G18" t="n">
-        <v>43.6378</v>
+        <v>38.8675</v>
       </c>
       <c r="H18" t="b">
         <v>0</v>
@@ -3770,16 +3770,16 @@
         <v>7</v>
       </c>
       <c r="D19" t="n">
-        <v>24.9389</v>
+        <v>15.4763</v>
       </c>
       <c r="E19" t="n">
         <v>0.9</v>
       </c>
       <c r="F19" t="n">
-        <v>-41.1553</v>
+        <v>-52.5837</v>
       </c>
       <c r="G19" t="n">
-        <v>91.0331</v>
+        <v>83.5364</v>
       </c>
       <c r="H19" t="b">
         <v>0</v>
@@ -3796,16 +3796,16 @@
         <v>8</v>
       </c>
       <c r="D20" t="n">
-        <v>-19.5153</v>
+        <v>-30.0237</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9</v>
+        <v>0.6732</v>
       </c>
       <c r="F20" t="n">
-        <v>-76.40009999999999</v>
+        <v>-88.60039999999999</v>
       </c>
       <c r="G20" t="n">
-        <v>37.3695</v>
+        <v>28.5531</v>
       </c>
       <c r="H20" t="b">
         <v>0</v>
@@ -3822,16 +3822,16 @@
         <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>-20.9678</v>
+        <v>-15.9542</v>
       </c>
       <c r="E21" t="n">
-        <v>0.8408</v>
+        <v>0.9</v>
       </c>
       <c r="F21" t="n">
-        <v>-70.884</v>
+        <v>-67.35509999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>28.9484</v>
+        <v>35.4467</v>
       </c>
       <c r="H21" t="b">
         <v>0</v>
@@ -3848,16 +3848,16 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>-27.9358</v>
+        <v>-19.5983</v>
       </c>
       <c r="E22" t="n">
-        <v>0.868</v>
+        <v>0.9</v>
       </c>
       <c r="F22" t="n">
-        <v>-96.9049</v>
+        <v>-90.61879999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>41.0334</v>
+        <v>51.4223</v>
       </c>
       <c r="H22" t="b">
         <v>0</v>
@@ -3874,16 +3874,16 @@
         <v>6</v>
       </c>
       <c r="D23" t="n">
-        <v>-17.2081</v>
+        <v>-3.1111</v>
       </c>
       <c r="E23" t="n">
         <v>0.9</v>
       </c>
       <c r="F23" t="n">
-        <v>-69.3439</v>
+        <v>-56.7976</v>
       </c>
       <c r="G23" t="n">
-        <v>34.9277</v>
+        <v>50.5754</v>
       </c>
       <c r="H23" t="b">
         <v>0</v>
@@ -3900,16 +3900,16 @@
         <v>7</v>
       </c>
       <c r="D24" t="n">
-        <v>12.3615</v>
+        <v>23.2017</v>
       </c>
       <c r="E24" t="n">
         <v>0.9</v>
       </c>
       <c r="F24" t="n">
-        <v>-56.6077</v>
+        <v>-47.8188</v>
       </c>
       <c r="G24" t="n">
-        <v>81.3306</v>
+        <v>94.2223</v>
       </c>
       <c r="H24" t="b">
         <v>0</v>
@@ -3926,16 +3926,16 @@
         <v>8</v>
       </c>
       <c r="D25" t="n">
-        <v>-32.0927</v>
+        <v>-22.2983</v>
       </c>
       <c r="E25" t="n">
-        <v>0.636</v>
+        <v>0.9</v>
       </c>
       <c r="F25" t="n">
-        <v>-92.294</v>
+        <v>-84.2901</v>
       </c>
       <c r="G25" t="n">
-        <v>28.1085</v>
+        <v>39.6935</v>
       </c>
       <c r="H25" t="b">
         <v>0</v>
@@ -3952,16 +3952,16 @@
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>-6.9679</v>
+        <v>-3.6441</v>
       </c>
       <c r="E26" t="n">
         <v>0.9</v>
       </c>
       <c r="F26" t="n">
-        <v>-74.27500000000001</v>
+        <v>-72.95310000000001</v>
       </c>
       <c r="G26" t="n">
-        <v>60.3391</v>
+        <v>65.6649</v>
       </c>
       <c r="H26" t="b">
         <v>0</v>
@@ -3978,16 +3978,16 @@
         <v>6</v>
       </c>
       <c r="D27" t="n">
-        <v>3.7598</v>
+        <v>12.8431</v>
       </c>
       <c r="E27" t="n">
         <v>0.9</v>
       </c>
       <c r="F27" t="n">
-        <v>-46.1565</v>
+        <v>-38.5578</v>
       </c>
       <c r="G27" t="n">
-        <v>53.676</v>
+        <v>64.244</v>
       </c>
       <c r="H27" t="b">
         <v>0</v>
@@ -4004,16 +4004,16 @@
         <v>7</v>
       </c>
       <c r="D28" t="n">
-        <v>33.3293</v>
+        <v>39.1559</v>
       </c>
       <c r="E28" t="n">
-        <v>0.7047</v>
+        <v>0.5783</v>
       </c>
       <c r="F28" t="n">
-        <v>-33.9777</v>
+        <v>-30.1531</v>
       </c>
       <c r="G28" t="n">
-        <v>100.6363</v>
+        <v>108.4649</v>
       </c>
       <c r="H28" t="b">
         <v>0</v>
@@ -4030,16 +4030,16 @@
         <v>8</v>
       </c>
       <c r="D29" t="n">
-        <v>-11.1249</v>
+        <v>-6.3441</v>
       </c>
       <c r="E29" t="n">
         <v>0.9</v>
       </c>
       <c r="F29" t="n">
-        <v>-69.4145</v>
+        <v>-66.3674</v>
       </c>
       <c r="G29" t="n">
-        <v>47.1647</v>
+        <v>53.6792</v>
       </c>
       <c r="H29" t="b">
         <v>0</v>
@@ -4056,16 +4056,16 @@
         <v>6</v>
       </c>
       <c r="D30" t="n">
-        <v>10.7277</v>
+        <v>16.4872</v>
       </c>
       <c r="E30" t="n">
         <v>0.9</v>
       </c>
       <c r="F30" t="n">
-        <v>-58.2415</v>
+        <v>-54.5334</v>
       </c>
       <c r="G30" t="n">
-        <v>79.6969</v>
+        <v>87.5077</v>
       </c>
       <c r="H30" t="b">
         <v>0</v>
@@ -4082,16 +4082,16 @@
         <v>7</v>
       </c>
       <c r="D31" t="n">
-        <v>40.2972</v>
+        <v>42.8</v>
       </c>
       <c r="E31" t="n">
-        <v>0.7161999999999999</v>
+        <v>0.6883</v>
       </c>
       <c r="F31" t="n">
-        <v>-42.1367</v>
+        <v>-42.0858</v>
       </c>
       <c r="G31" t="n">
-        <v>122.7311</v>
+        <v>127.6858</v>
       </c>
       <c r="H31" t="b">
         <v>0</v>
@@ -4108,16 +4108,16 @@
         <v>8</v>
       </c>
       <c r="D32" t="n">
-        <v>-4.157</v>
+        <v>-2.7</v>
       </c>
       <c r="E32" t="n">
         <v>0.9</v>
       </c>
       <c r="F32" t="n">
-        <v>-79.4085</v>
+        <v>-80.18980000000001</v>
       </c>
       <c r="G32" t="n">
-        <v>71.0946</v>
+        <v>74.7898</v>
       </c>
       <c r="H32" t="b">
         <v>0</v>
@@ -4134,16 +4134,16 @@
         <v>7</v>
       </c>
       <c r="D33" t="n">
-        <v>29.5695</v>
+        <v>26.3128</v>
       </c>
       <c r="E33" t="n">
-        <v>0.8250999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="F33" t="n">
-        <v>-39.3997</v>
+        <v>-44.7077</v>
       </c>
       <c r="G33" t="n">
-        <v>98.53870000000001</v>
+        <v>97.3334</v>
       </c>
       <c r="H33" t="b">
         <v>0</v>
@@ -4160,16 +4160,16 @@
         <v>8</v>
       </c>
       <c r="D34" t="n">
-        <v>-14.8847</v>
+        <v>-19.1872</v>
       </c>
       <c r="E34" t="n">
         <v>0.9</v>
       </c>
       <c r="F34" t="n">
-        <v>-75.0859</v>
+        <v>-81.179</v>
       </c>
       <c r="G34" t="n">
-        <v>45.3166</v>
+        <v>42.8046</v>
       </c>
       <c r="H34" t="b">
         <v>0</v>
@@ -4186,16 +4186,16 @@
         <v>8</v>
       </c>
       <c r="D35" t="n">
-        <v>-44.4542</v>
+        <v>-45.5</v>
       </c>
       <c r="E35" t="n">
-        <v>0.5315</v>
+        <v>0.538</v>
       </c>
       <c r="F35" t="n">
-        <v>-119.7057</v>
+        <v>-122.9898</v>
       </c>
       <c r="G35" t="n">
-        <v>30.7973</v>
+        <v>31.9898</v>
       </c>
       <c r="H35" t="b">
         <v>0</v>
@@ -4267,16 +4267,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.6482</v>
+        <v>0.5582</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7371</v>
+        <v>0.4936</v>
       </c>
       <c r="F2" t="n">
-        <v>-4.3661</v>
+        <v>-1.0737</v>
       </c>
       <c r="G2" t="n">
-        <v>3.0697</v>
+        <v>2.19</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
@@ -4297,16 +4297,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-2.3352</v>
+        <v>-1.0061</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2108</v>
+        <v>0.2215</v>
       </c>
       <c r="F3" t="n">
-        <v>-6.0448</v>
+        <v>-2.6427</v>
       </c>
       <c r="G3" t="n">
-        <v>1.3745</v>
+        <v>0.6304999999999999</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
@@ -4327,16 +4327,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.8717</v>
+        <v>-0.8485</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3067</v>
+        <v>0.293</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.7802</v>
+        <v>-2.457</v>
       </c>
       <c r="G4" t="n">
-        <v>5.5236</v>
+        <v>0.76</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
@@ -4357,16 +4357,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.9992</v>
+        <v>-0.3538</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5986</v>
+        <v>0.6763</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.711</v>
+        <v>-1.9913</v>
       </c>
       <c r="G5" t="n">
-        <v>4.7094</v>
+        <v>1.2837</v>
       </c>
       <c r="H5" t="b">
         <v>0</v>
@@ -4383,16 +4383,16 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2775</v>
+        <v>0.8961</v>
       </c>
       <c r="E6" t="n">
         <v>0.9</v>
       </c>
       <c r="F6" t="n">
-        <v>-14.1214</v>
+        <v>-5.5311</v>
       </c>
       <c r="G6" t="n">
-        <v>14.6763</v>
+        <v>7.3233</v>
       </c>
       <c r="H6" t="b">
         <v>0</v>
@@ -4409,16 +4409,16 @@
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>2.4426</v>
+        <v>0.1549</v>
       </c>
       <c r="E7" t="n">
         <v>0.9</v>
       </c>
       <c r="F7" t="n">
-        <v>-10.0271</v>
+        <v>-5.4113</v>
       </c>
       <c r="G7" t="n">
-        <v>14.9124</v>
+        <v>5.721</v>
       </c>
       <c r="H7" t="b">
         <v>0</v>
@@ -4435,16 +4435,16 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>1.4446</v>
+        <v>0.4263</v>
       </c>
       <c r="E8" t="n">
         <v>0.9</v>
       </c>
       <c r="F8" t="n">
-        <v>-11.7816</v>
+        <v>-5.4775</v>
       </c>
       <c r="G8" t="n">
-        <v>14.6707</v>
+        <v>6.3301</v>
       </c>
       <c r="H8" t="b">
         <v>0</v>
@@ -4461,16 +4461,16 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>2.2059</v>
+        <v>1.6262</v>
       </c>
       <c r="E9" t="n">
         <v>0.9</v>
       </c>
       <c r="F9" t="n">
-        <v>-9.0342</v>
+        <v>-3.391</v>
       </c>
       <c r="G9" t="n">
-        <v>13.4459</v>
+        <v>6.6435</v>
       </c>
       <c r="H9" t="b">
         <v>0</v>
@@ -4487,16 +4487,16 @@
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>2.8631</v>
+        <v>2.5154</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9</v>
+        <v>0.8026</v>
       </c>
       <c r="F10" t="n">
-        <v>-9.6066</v>
+        <v>-3.0507</v>
       </c>
       <c r="G10" t="n">
-        <v>15.3328</v>
+        <v>8.0816</v>
       </c>
       <c r="H10" t="b">
         <v>0</v>
@@ -4513,16 +4513,16 @@
         <v>7</v>
       </c>
       <c r="D11" t="n">
-        <v>6.8664</v>
+        <v>0.7267</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5793</v>
+        <v>0.9</v>
       </c>
       <c r="F11" t="n">
-        <v>-5.0725</v>
+        <v>-4.6025</v>
       </c>
       <c r="G11" t="n">
-        <v>18.8053</v>
+        <v>6.0559</v>
       </c>
       <c r="H11" t="b">
         <v>0</v>
@@ -4539,16 +4539,16 @@
         <v>8</v>
       </c>
       <c r="D12" t="n">
-        <v>2.3348</v>
+        <v>0.588</v>
       </c>
       <c r="E12" t="n">
         <v>0.9</v>
       </c>
       <c r="F12" t="n">
-        <v>-9.210000000000001</v>
+        <v>-4.5652</v>
       </c>
       <c r="G12" t="n">
-        <v>13.8795</v>
+        <v>5.7413</v>
       </c>
       <c r="H12" t="b">
         <v>0</v>
@@ -4565,16 +4565,16 @@
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>2.1652</v>
+        <v>-0.7412</v>
       </c>
       <c r="E13" t="n">
         <v>0.9</v>
       </c>
       <c r="F13" t="n">
-        <v>-12.2336</v>
+        <v>-7.1685</v>
       </c>
       <c r="G13" t="n">
-        <v>16.564</v>
+        <v>5.686</v>
       </c>
       <c r="H13" t="b">
         <v>0</v>
@@ -4591,16 +4591,16 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>1.1671</v>
+        <v>-0.4698</v>
       </c>
       <c r="E14" t="n">
         <v>0.9</v>
       </c>
       <c r="F14" t="n">
-        <v>-13.8915</v>
+        <v>-7.1916</v>
       </c>
       <c r="G14" t="n">
-        <v>16.2258</v>
+        <v>6.2519</v>
       </c>
       <c r="H14" t="b">
         <v>0</v>
@@ -4617,16 +4617,16 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>1.9284</v>
+        <v>0.7301</v>
       </c>
       <c r="E15" t="n">
         <v>0.9</v>
       </c>
       <c r="F15" t="n">
-        <v>-11.4196</v>
+        <v>-5.2281</v>
       </c>
       <c r="G15" t="n">
-        <v>15.2765</v>
+        <v>6.6883</v>
       </c>
       <c r="H15" t="b">
         <v>0</v>
@@ -4643,16 +4643,16 @@
         <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>2.5856</v>
+        <v>1.6193</v>
       </c>
       <c r="E16" t="n">
         <v>0.9</v>
       </c>
       <c r="F16" t="n">
-        <v>-11.8132</v>
+        <v>-4.8079</v>
       </c>
       <c r="G16" t="n">
-        <v>16.9845</v>
+        <v>8.0466</v>
       </c>
       <c r="H16" t="b">
         <v>0</v>
@@ -4669,16 +4669,16 @@
         <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>6.5889</v>
+        <v>-0.1694</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7651</v>
+        <v>0.9</v>
       </c>
       <c r="F17" t="n">
-        <v>-7.3526</v>
+        <v>-6.3926</v>
       </c>
       <c r="G17" t="n">
-        <v>20.5305</v>
+        <v>6.0537</v>
       </c>
       <c r="H17" t="b">
         <v>0</v>
@@ -4695,16 +4695,16 @@
         <v>8</v>
       </c>
       <c r="D18" t="n">
-        <v>2.0573</v>
+        <v>-0.3081</v>
       </c>
       <c r="E18" t="n">
         <v>0.9</v>
       </c>
       <c r="F18" t="n">
-        <v>-11.5483</v>
+        <v>-6.3812</v>
       </c>
       <c r="G18" t="n">
-        <v>15.6629</v>
+        <v>5.7651</v>
       </c>
       <c r="H18" t="b">
         <v>0</v>
@@ -4721,16 +4721,16 @@
         <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.998</v>
+        <v>0.2714</v>
       </c>
       <c r="E19" t="n">
         <v>0.9</v>
       </c>
       <c r="F19" t="n">
-        <v>-14.2242</v>
+        <v>-5.6324</v>
       </c>
       <c r="G19" t="n">
-        <v>12.2281</v>
+        <v>6.1752</v>
       </c>
       <c r="H19" t="b">
         <v>0</v>
@@ -4747,16 +4747,16 @@
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2368</v>
+        <v>1.4714</v>
       </c>
       <c r="E20" t="n">
         <v>0.9</v>
       </c>
       <c r="F20" t="n">
-        <v>-11.4768</v>
+        <v>-3.5459</v>
       </c>
       <c r="G20" t="n">
-        <v>11.0033</v>
+        <v>6.4886</v>
       </c>
       <c r="H20" t="b">
         <v>0</v>
@@ -4773,16 +4773,16 @@
         <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>0.4205</v>
+        <v>2.3606</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9</v>
+        <v>0.853</v>
       </c>
       <c r="F21" t="n">
-        <v>-12.0493</v>
+        <v>-3.2056</v>
       </c>
       <c r="G21" t="n">
-        <v>12.8902</v>
+        <v>7.9267</v>
       </c>
       <c r="H21" t="b">
         <v>0</v>
@@ -4799,16 +4799,16 @@
         <v>7</v>
       </c>
       <c r="D22" t="n">
-        <v>4.4238</v>
+        <v>0.5718</v>
       </c>
       <c r="E22" t="n">
         <v>0.9</v>
       </c>
       <c r="F22" t="n">
-        <v>-7.5151</v>
+        <v>-4.7574</v>
       </c>
       <c r="G22" t="n">
-        <v>16.3626</v>
+        <v>5.901</v>
       </c>
       <c r="H22" t="b">
         <v>0</v>
@@ -4825,16 +4825,16 @@
         <v>8</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1079</v>
+        <v>0.4332</v>
       </c>
       <c r="E23" t="n">
         <v>0.9</v>
       </c>
       <c r="F23" t="n">
-        <v>-11.6526</v>
+        <v>-4.7201</v>
       </c>
       <c r="G23" t="n">
-        <v>11.4369</v>
+        <v>5.5864</v>
       </c>
       <c r="H23" t="b">
         <v>0</v>
@@ -4851,16 +4851,16 @@
         <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>0.7613</v>
+        <v>1.2</v>
       </c>
       <c r="E24" t="n">
         <v>0.9</v>
       </c>
       <c r="F24" t="n">
-        <v>-11.3125</v>
+        <v>-4.1895</v>
       </c>
       <c r="G24" t="n">
-        <v>12.835</v>
+        <v>6.5894</v>
       </c>
       <c r="H24" t="b">
         <v>0</v>
@@ -4877,16 +4877,16 @@
         <v>6</v>
       </c>
       <c r="D25" t="n">
-        <v>1.4185</v>
+        <v>2.0892</v>
       </c>
       <c r="E25" t="n">
         <v>0.9</v>
       </c>
       <c r="F25" t="n">
-        <v>-11.8077</v>
+        <v>-3.8146</v>
       </c>
       <c r="G25" t="n">
-        <v>14.6446</v>
+        <v>7.993</v>
       </c>
       <c r="H25" t="b">
         <v>0</v>
@@ -4903,16 +4903,16 @@
         <v>7</v>
       </c>
       <c r="D26" t="n">
-        <v>5.4218</v>
+        <v>0.3004</v>
       </c>
       <c r="E26" t="n">
-        <v>0.8495</v>
+        <v>0.9</v>
       </c>
       <c r="F26" t="n">
-        <v>-7.3051</v>
+        <v>-5.3805</v>
       </c>
       <c r="G26" t="n">
-        <v>18.1487</v>
+        <v>5.9813</v>
       </c>
       <c r="H26" t="b">
         <v>0</v>
@@ -4929,16 +4929,16 @@
         <v>8</v>
       </c>
       <c r="D27" t="n">
-        <v>0.8902</v>
+        <v>0.1618</v>
       </c>
       <c r="E27" t="n">
         <v>0.9</v>
       </c>
       <c r="F27" t="n">
-        <v>-11.4677</v>
+        <v>-5.3545</v>
       </c>
       <c r="G27" t="n">
-        <v>13.2481</v>
+        <v>5.678</v>
       </c>
       <c r="H27" t="b">
         <v>0</v>
@@ -4955,16 +4955,16 @@
         <v>6</v>
       </c>
       <c r="D28" t="n">
-        <v>0.6572</v>
+        <v>0.8892</v>
       </c>
       <c r="E28" t="n">
         <v>0.9</v>
       </c>
       <c r="F28" t="n">
-        <v>-10.5828</v>
+        <v>-4.128</v>
       </c>
       <c r="G28" t="n">
-        <v>11.8973</v>
+        <v>5.9065</v>
       </c>
       <c r="H28" t="b">
         <v>0</v>
@@ -4981,16 +4981,16 @@
         <v>7</v>
       </c>
       <c r="D29" t="n">
-        <v>4.6605</v>
+        <v>-0.8995</v>
       </c>
       <c r="E29" t="n">
-        <v>0.8284</v>
+        <v>0.9</v>
       </c>
       <c r="F29" t="n">
-        <v>-5.9875</v>
+        <v>-5.6525</v>
       </c>
       <c r="G29" t="n">
-        <v>15.3086</v>
+        <v>3.8535</v>
       </c>
       <c r="H29" t="b">
         <v>0</v>
@@ -5007,16 +5007,16 @@
         <v>8</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1289</v>
+        <v>-1.0382</v>
       </c>
       <c r="E30" t="n">
         <v>0.9</v>
       </c>
       <c r="F30" t="n">
-        <v>-10.0753</v>
+        <v>-5.5931</v>
       </c>
       <c r="G30" t="n">
-        <v>10.3331</v>
+        <v>3.5167</v>
       </c>
       <c r="H30" t="b">
         <v>0</v>
@@ -5033,16 +5033,16 @@
         <v>7</v>
       </c>
       <c r="D31" t="n">
-        <v>4.0033</v>
+        <v>-1.7888</v>
       </c>
       <c r="E31" t="n">
         <v>0.9</v>
       </c>
       <c r="F31" t="n">
-        <v>-7.9356</v>
+        <v>-7.1179</v>
       </c>
       <c r="G31" t="n">
-        <v>15.9422</v>
+        <v>3.5404</v>
       </c>
       <c r="H31" t="b">
         <v>0</v>
@@ -5059,16 +5059,16 @@
         <v>8</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.5283</v>
+        <v>-1.9274</v>
       </c>
       <c r="E32" t="n">
         <v>0.9</v>
       </c>
       <c r="F32" t="n">
-        <v>-12.073</v>
+        <v>-7.0807</v>
       </c>
       <c r="G32" t="n">
-        <v>11.0164</v>
+        <v>3.2258</v>
       </c>
       <c r="H32" t="b">
         <v>0</v>
@@ -5085,16 +5085,16 @@
         <v>8</v>
       </c>
       <c r="D33" t="n">
-        <v>-4.5316</v>
+        <v>-0.1387</v>
       </c>
       <c r="E33" t="n">
-        <v>0.8729</v>
+        <v>0.9</v>
       </c>
       <c r="F33" t="n">
-        <v>-15.5008</v>
+        <v>-5.035</v>
       </c>
       <c r="G33" t="n">
-        <v>6.4376</v>
+        <v>4.7577</v>
       </c>
       <c r="H33" t="b">
         <v>0</v>
@@ -5166,16 +5166,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>8.4838</v>
+        <v>14.1743</v>
       </c>
       <c r="E2" t="n">
-        <v>0.398</v>
+        <v>0.1512</v>
       </c>
       <c r="F2" t="n">
-        <v>-11.5778</v>
+        <v>-5.398</v>
       </c>
       <c r="G2" t="n">
-        <v>28.5454</v>
+        <v>33.7466</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
@@ -5196,16 +5196,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>10.0174</v>
+        <v>-2.2161</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3251</v>
+        <v>0.8327</v>
       </c>
       <c r="F3" t="n">
-        <v>-10.2956</v>
+        <v>-22.5959</v>
       </c>
       <c r="G3" t="n">
-        <v>30.3305</v>
+        <v>18.1638</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
@@ -5226,16 +5226,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.5319</v>
+        <v>-0.7808</v>
       </c>
       <c r="E4" t="n">
         <v>0.9</v>
       </c>
       <c r="F4" t="n">
-        <v>-19.5748</v>
+        <v>-20.7248</v>
       </c>
       <c r="G4" t="n">
-        <v>20.6386</v>
+        <v>19.1633</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
@@ -5256,16 +5256,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4.6461</v>
+        <v>-7.3311</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6556999999999999</v>
+        <v>0.4621</v>
       </c>
       <c r="F5" t="n">
-        <v>-15.54</v>
+        <v>-27.2739</v>
       </c>
       <c r="G5" t="n">
-        <v>24.8323</v>
+        <v>12.6116</v>
       </c>
       <c r="H5" t="b">
         <v>0</v>
@@ -5282,16 +5282,16 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>-3.1836</v>
+        <v>9.7034</v>
       </c>
       <c r="E6" t="n">
         <v>0.9</v>
       </c>
       <c r="F6" t="n">
-        <v>-81.26439999999999</v>
+        <v>-69.02030000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>74.8972</v>
+        <v>88.4271</v>
       </c>
       <c r="H6" t="b">
         <v>0</v>
@@ -5308,16 +5308,16 @@
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>23.5566</v>
+        <v>23.4752</v>
       </c>
       <c r="E7" t="n">
         <v>0.9</v>
       </c>
       <c r="F7" t="n">
-        <v>-44.0634</v>
+        <v>-44.7016</v>
       </c>
       <c r="G7" t="n">
-        <v>91.1765</v>
+        <v>91.6519</v>
       </c>
       <c r="H7" t="b">
         <v>0</v>
@@ -5334,16 +5334,16 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>2.5168</v>
+        <v>14.4128</v>
       </c>
       <c r="E8" t="n">
         <v>0.9</v>
       </c>
       <c r="F8" t="n">
-        <v>-69.205</v>
+        <v>-57.8996</v>
       </c>
       <c r="G8" t="n">
-        <v>74.2385</v>
+        <v>86.7251</v>
       </c>
       <c r="H8" t="b">
         <v>0</v>
@@ -5360,16 +5360,16 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>6.8521</v>
+        <v>17.3874</v>
       </c>
       <c r="E9" t="n">
         <v>0.9</v>
       </c>
       <c r="F9" t="n">
-        <v>-54.0997</v>
+        <v>-44.0663</v>
       </c>
       <c r="G9" t="n">
-        <v>67.8038</v>
+        <v>78.8411</v>
       </c>
       <c r="H9" t="b">
         <v>0</v>
@@ -5386,16 +5386,16 @@
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>-6.4089</v>
+        <v>24.0976</v>
       </c>
       <c r="E10" t="n">
         <v>0.9</v>
       </c>
       <c r="F10" t="n">
-        <v>-74.02889999999999</v>
+        <v>-44.0792</v>
       </c>
       <c r="G10" t="n">
-        <v>61.211</v>
+        <v>92.2743</v>
       </c>
       <c r="H10" t="b">
         <v>0</v>
@@ -5412,16 +5412,16 @@
         <v>7</v>
       </c>
       <c r="D11" t="n">
-        <v>-16.9479</v>
+        <v>-2.3111</v>
       </c>
       <c r="E11" t="n">
         <v>0.9</v>
       </c>
       <c r="F11" t="n">
-        <v>-81.6891</v>
+        <v>-67.58540000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>47.7932</v>
+        <v>62.9631</v>
       </c>
       <c r="H11" t="b">
         <v>0</v>
@@ -5438,16 +5438,16 @@
         <v>8</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.0871</v>
+        <v>17.7296</v>
       </c>
       <c r="E12" t="n">
         <v>0.9</v>
       </c>
       <c r="F12" t="n">
-        <v>-62.691</v>
+        <v>-45.3898</v>
       </c>
       <c r="G12" t="n">
-        <v>62.5168</v>
+        <v>80.849</v>
       </c>
       <c r="H12" t="b">
         <v>0</v>
@@ -5464,16 +5464,16 @@
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>26.7402</v>
+        <v>13.7718</v>
       </c>
       <c r="E13" t="n">
         <v>0.9</v>
       </c>
       <c r="F13" t="n">
-        <v>-51.3406</v>
+        <v>-64.95189999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>104.8209</v>
+        <v>92.49550000000001</v>
       </c>
       <c r="H13" t="b">
         <v>0</v>
@@ -5490,16 +5490,16 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>5.7004</v>
+        <v>4.7094</v>
       </c>
       <c r="E14" t="n">
         <v>0.9</v>
       </c>
       <c r="F14" t="n">
-        <v>-75.9585</v>
+        <v>-77.62179999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>87.3592</v>
+        <v>87.0407</v>
       </c>
       <c r="H14" t="b">
         <v>0</v>
@@ -5516,16 +5516,16 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>10.0357</v>
+        <v>7.684</v>
       </c>
       <c r="E15" t="n">
         <v>0.9</v>
       </c>
       <c r="F15" t="n">
-        <v>-62.3471</v>
+        <v>-65.2948</v>
       </c>
       <c r="G15" t="n">
-        <v>82.41849999999999</v>
+        <v>80.66289999999999</v>
       </c>
       <c r="H15" t="b">
         <v>0</v>
@@ -5542,16 +5542,16 @@
         <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>-3.2253</v>
+        <v>14.3942</v>
       </c>
       <c r="E16" t="n">
         <v>0.9</v>
       </c>
       <c r="F16" t="n">
-        <v>-81.3061</v>
+        <v>-64.3295</v>
       </c>
       <c r="G16" t="n">
-        <v>74.8554</v>
+        <v>93.11790000000001</v>
       </c>
       <c r="H16" t="b">
         <v>0</v>
@@ -5568,16 +5568,16 @@
         <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>-13.7643</v>
+        <v>-12.0145</v>
       </c>
       <c r="E17" t="n">
         <v>0.9</v>
       </c>
       <c r="F17" t="n">
-        <v>-89.3657</v>
+        <v>-88.2384</v>
       </c>
       <c r="G17" t="n">
-        <v>61.837</v>
+        <v>64.2094</v>
       </c>
       <c r="H17" t="b">
         <v>0</v>
@@ -5594,16 +5594,16 @@
         <v>8</v>
       </c>
       <c r="D18" t="n">
-        <v>3.0965</v>
+        <v>8.026199999999999</v>
       </c>
       <c r="E18" t="n">
         <v>0.9</v>
       </c>
       <c r="F18" t="n">
-        <v>-70.6829</v>
+        <v>-66.36069999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>76.8759</v>
+        <v>82.4132</v>
       </c>
       <c r="H18" t="b">
         <v>0</v>
@@ -5620,16 +5620,16 @@
         <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>-21.0398</v>
+        <v>-9.0624</v>
       </c>
       <c r="E19" t="n">
         <v>0.9</v>
       </c>
       <c r="F19" t="n">
-        <v>-92.7616</v>
+        <v>-81.3747</v>
       </c>
       <c r="G19" t="n">
-        <v>50.682</v>
+        <v>63.25</v>
       </c>
       <c r="H19" t="b">
         <v>0</v>
@@ -5646,16 +5646,16 @@
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>-16.7045</v>
+        <v>-6.0877</v>
       </c>
       <c r="E20" t="n">
         <v>0.9</v>
       </c>
       <c r="F20" t="n">
-        <v>-77.6563</v>
+        <v>-67.5414</v>
       </c>
       <c r="G20" t="n">
-        <v>44.2473</v>
+        <v>55.3659</v>
       </c>
       <c r="H20" t="b">
         <v>0</v>
@@ -5672,16 +5672,16 @@
         <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>-29.9655</v>
+        <v>0.6224</v>
       </c>
       <c r="E21" t="n">
-        <v>0.8185</v>
+        <v>0.9</v>
       </c>
       <c r="F21" t="n">
-        <v>-97.58540000000001</v>
+        <v>-67.5543</v>
       </c>
       <c r="G21" t="n">
-        <v>37.6544</v>
+        <v>68.7991</v>
       </c>
       <c r="H21" t="b">
         <v>0</v>
@@ -5698,16 +5698,16 @@
         <v>7</v>
       </c>
       <c r="D22" t="n">
-        <v>-40.5045</v>
+        <v>-25.7863</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4875</v>
+        <v>0.9</v>
       </c>
       <c r="F22" t="n">
-        <v>-105.2457</v>
+        <v>-91.0605</v>
       </c>
       <c r="G22" t="n">
-        <v>24.2367</v>
+        <v>39.488</v>
       </c>
       <c r="H22" t="b">
         <v>0</v>
@@ -5724,16 +5724,16 @@
         <v>8</v>
       </c>
       <c r="D23" t="n">
-        <v>-23.6437</v>
+        <v>-5.7455</v>
       </c>
       <c r="E23" t="n">
         <v>0.9</v>
       </c>
       <c r="F23" t="n">
-        <v>-86.24760000000001</v>
+        <v>-68.86490000000001</v>
       </c>
       <c r="G23" t="n">
-        <v>38.9602</v>
+        <v>57.3738</v>
       </c>
       <c r="H23" t="b">
         <v>0</v>
@@ -5750,16 +5750,16 @@
         <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>4.3353</v>
+        <v>2.9746</v>
       </c>
       <c r="E24" t="n">
         <v>0.9</v>
       </c>
       <c r="F24" t="n">
-        <v>-61.1374</v>
+        <v>-63.0372</v>
       </c>
       <c r="G24" t="n">
-        <v>69.80800000000001</v>
+        <v>68.98650000000001</v>
       </c>
       <c r="H24" t="b">
         <v>0</v>
@@ -5776,16 +5776,16 @@
         <v>6</v>
       </c>
       <c r="D25" t="n">
-        <v>-8.925700000000001</v>
+        <v>9.684799999999999</v>
       </c>
       <c r="E25" t="n">
         <v>0.9</v>
       </c>
       <c r="F25" t="n">
-        <v>-80.64749999999999</v>
+        <v>-62.6276</v>
       </c>
       <c r="G25" t="n">
-        <v>62.7961</v>
+        <v>81.9971</v>
       </c>
       <c r="H25" t="b">
         <v>0</v>
@@ -5802,16 +5802,16 @@
         <v>7</v>
       </c>
       <c r="D26" t="n">
-        <v>-19.4647</v>
+        <v>-16.7239</v>
       </c>
       <c r="E26" t="n">
         <v>0.9</v>
       </c>
       <c r="F26" t="n">
-        <v>-88.479</v>
+        <v>-86.3065</v>
       </c>
       <c r="G26" t="n">
-        <v>49.5496</v>
+        <v>52.8587</v>
       </c>
       <c r="H26" t="b">
         <v>0</v>
@@ -5828,16 +5828,16 @@
         <v>8</v>
       </c>
       <c r="D27" t="n">
-        <v>-2.6039</v>
+        <v>3.3168</v>
       </c>
       <c r="E27" t="n">
         <v>0.9</v>
       </c>
       <c r="F27" t="n">
-        <v>-69.6173</v>
+        <v>-64.24850000000001</v>
       </c>
       <c r="G27" t="n">
-        <v>64.4096</v>
+        <v>70.88209999999999</v>
       </c>
       <c r="H27" t="b">
         <v>0</v>
@@ -5854,16 +5854,16 @@
         <v>6</v>
       </c>
       <c r="D28" t="n">
-        <v>-13.261</v>
+        <v>6.7102</v>
       </c>
       <c r="E28" t="n">
         <v>0.9</v>
       </c>
       <c r="F28" t="n">
-        <v>-74.2128</v>
+        <v>-54.7435</v>
       </c>
       <c r="G28" t="n">
-        <v>47.6908</v>
+        <v>68.16379999999999</v>
       </c>
       <c r="H28" t="b">
         <v>0</v>
@@ -5880,16 +5880,16 @@
         <v>7</v>
       </c>
       <c r="D29" t="n">
-        <v>-23.8</v>
+        <v>-19.6985</v>
       </c>
       <c r="E29" t="n">
-        <v>0.8746</v>
+        <v>0.9</v>
       </c>
       <c r="F29" t="n">
-        <v>-81.5415</v>
+        <v>-77.91549999999999</v>
       </c>
       <c r="G29" t="n">
-        <v>33.9415</v>
+        <v>38.5184</v>
       </c>
       <c r="H29" t="b">
         <v>0</v>
@@ -5906,16 +5906,16 @@
         <v>8</v>
       </c>
       <c r="D30" t="n">
-        <v>-6.9392</v>
+        <v>0.3422</v>
       </c>
       <c r="E30" t="n">
         <v>0.9</v>
       </c>
       <c r="F30" t="n">
-        <v>-62.2737</v>
+        <v>-55.448</v>
       </c>
       <c r="G30" t="n">
-        <v>48.3954</v>
+        <v>56.1324</v>
       </c>
       <c r="H30" t="b">
         <v>0</v>
@@ -5932,16 +5932,16 @@
         <v>7</v>
       </c>
       <c r="D31" t="n">
-        <v>-10.539</v>
+        <v>-26.4087</v>
       </c>
       <c r="E31" t="n">
-        <v>0.9</v>
+        <v>0.8883</v>
       </c>
       <c r="F31" t="n">
-        <v>-75.28019999999999</v>
+        <v>-91.6829</v>
       </c>
       <c r="G31" t="n">
-        <v>54.2021</v>
+        <v>38.8656</v>
       </c>
       <c r="H31" t="b">
         <v>0</v>
@@ -5958,16 +5958,16 @@
         <v>8</v>
       </c>
       <c r="D32" t="n">
-        <v>6.3218</v>
+        <v>-6.368</v>
       </c>
       <c r="E32" t="n">
         <v>0.9</v>
       </c>
       <c r="F32" t="n">
-        <v>-56.2821</v>
+        <v>-69.4873</v>
       </c>
       <c r="G32" t="n">
-        <v>68.92570000000001</v>
+        <v>56.7514</v>
       </c>
       <c r="H32" t="b">
         <v>0</v>
@@ -5984,16 +5984,16 @@
         <v>8</v>
       </c>
       <c r="D33" t="n">
-        <v>16.8608</v>
+        <v>20.0407</v>
       </c>
       <c r="E33" t="n">
         <v>0.9</v>
       </c>
       <c r="F33" t="n">
-        <v>-42.622</v>
+        <v>-39.9319</v>
       </c>
       <c r="G33" t="n">
-        <v>76.3437</v>
+        <v>80.0134</v>
       </c>
       <c r="H33" t="b">
         <v>0</v>
@@ -6065,16 +6065,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.3563</v>
+        <v>-0.2802</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4254</v>
+        <v>0.1412</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.2502</v>
+        <v>-0.6574</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5375</v>
+        <v>0.0969</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
@@ -6095,16 +6095,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.0945</v>
+        <v>-0.0485</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8407</v>
+        <v>0.8113</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.8201000000000001</v>
+        <v>-0.4417</v>
       </c>
       <c r="G3" t="n">
-        <v>1.0091</v>
+        <v>0.3446</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
@@ -6125,16 +6125,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.7256</v>
+        <v>0.0236</v>
       </c>
       <c r="E4" t="n">
-        <v>0.098</v>
+        <v>0.9</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.5908</v>
+        <v>-0.3612</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1397</v>
+        <v>0.4083</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
@@ -6155,16 +6155,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.3993</v>
+        <v>0.1301</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3713</v>
+        <v>0.4991</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.4927</v>
+        <v>-0.2551</v>
       </c>
       <c r="G5" t="n">
-        <v>1.2914</v>
+        <v>0.5152</v>
       </c>
       <c r="H5" t="b">
         <v>0</v>
@@ -6181,16 +6181,16 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.5527</v>
+        <v>-0.2701</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7689</v>
+        <v>0.9</v>
       </c>
       <c r="F6" t="n">
-        <v>-4.853</v>
+        <v>-1.6375</v>
       </c>
       <c r="G6" t="n">
-        <v>1.7475</v>
+        <v>1.0973</v>
       </c>
       <c r="H6" t="b">
         <v>0</v>
@@ -6207,16 +6207,16 @@
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.4605</v>
+        <v>-0.8336</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1347</v>
+        <v>0.3395</v>
       </c>
       <c r="F7" t="n">
-        <v>-5.3187</v>
+        <v>-2.0179</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3976</v>
+        <v>0.3506</v>
       </c>
       <c r="H7" t="b">
         <v>0</v>
@@ -6233,16 +6233,16 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.3695</v>
+        <v>-0.0192</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8028999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="F8" t="n">
-        <v>-4.401</v>
+        <v>-1.2753</v>
       </c>
       <c r="G8" t="n">
-        <v>1.662</v>
+        <v>1.2368</v>
       </c>
       <c r="H8" t="b">
         <v>0</v>
@@ -6259,16 +6259,16 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.0236</v>
+        <v>-0.1609</v>
       </c>
       <c r="E9" t="n">
         <v>0.9</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.5999</v>
+        <v>-1.2283</v>
       </c>
       <c r="G9" t="n">
-        <v>1.5526</v>
+        <v>0.9066</v>
       </c>
       <c r="H9" t="b">
         <v>0</v>
@@ -6285,16 +6285,16 @@
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.6551</v>
+        <v>-0.7569</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5722</v>
+        <v>0.4619</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.5132</v>
+        <v>-1.9411</v>
       </c>
       <c r="G10" t="n">
-        <v>1.2031</v>
+        <v>0.4274</v>
       </c>
       <c r="H10" t="b">
         <v>0</v>
@@ -6311,16 +6311,16 @@
         <v>7</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.3872</v>
+        <v>0.067</v>
       </c>
       <c r="E11" t="n">
-        <v>0.7029</v>
+        <v>0.9</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.1236</v>
+        <v>-1.0669</v>
       </c>
       <c r="G11" t="n">
-        <v>1.3493</v>
+        <v>1.2008</v>
       </c>
       <c r="H11" t="b">
         <v>0</v>
@@ -6337,16 +6337,16 @@
         <v>8</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.7125</v>
+        <v>-0.2572</v>
       </c>
       <c r="E12" t="n">
-        <v>0.4464</v>
+        <v>0.9</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.3586</v>
+        <v>-1.3536</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9336</v>
+        <v>0.8391999999999999</v>
       </c>
       <c r="H12" t="b">
         <v>0</v>
@@ -6363,16 +6363,16 @@
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.9078000000000001</v>
+        <v>-0.5635</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9</v>
+        <v>0.8747</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.2081</v>
+        <v>-1.931</v>
       </c>
       <c r="G13" t="n">
-        <v>2.3925</v>
+        <v>0.8038999999999999</v>
       </c>
       <c r="H13" t="b">
         <v>0</v>
@@ -6389,16 +6389,16 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1833</v>
+        <v>0.2509</v>
       </c>
       <c r="E14" t="n">
         <v>0.9</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.2683</v>
+        <v>-1.1792</v>
       </c>
       <c r="G14" t="n">
-        <v>3.6348</v>
+        <v>1.681</v>
       </c>
       <c r="H14" t="b">
         <v>0</v>
@@ -6415,16 +6415,16 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5291</v>
+        <v>0.1092</v>
       </c>
       <c r="E15" t="n">
         <v>0.9</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.5303</v>
+        <v>-1.1584</v>
       </c>
       <c r="G15" t="n">
-        <v>3.5885</v>
+        <v>1.3769</v>
       </c>
       <c r="H15" t="b">
         <v>0</v>
@@ -6441,16 +6441,16 @@
         <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1023</v>
+        <v>-0.4868</v>
       </c>
       <c r="E16" t="n">
         <v>0.9</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.4026</v>
+        <v>-1.8542</v>
       </c>
       <c r="G16" t="n">
-        <v>3.198</v>
+        <v>0.8807</v>
       </c>
       <c r="H16" t="b">
         <v>0</v>
@@ -6467,16 +6467,16 @@
         <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1656</v>
+        <v>0.3371</v>
       </c>
       <c r="E17" t="n">
         <v>0.9</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.0299</v>
+        <v>-0.987</v>
       </c>
       <c r="G17" t="n">
-        <v>3.3611</v>
+        <v>1.6611</v>
       </c>
       <c r="H17" t="b">
         <v>0</v>
@@ -6493,16 +6493,16 @@
         <v>8</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1597</v>
+        <v>0.0129</v>
       </c>
       <c r="E18" t="n">
         <v>0.9</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.2782</v>
+        <v>-1.2792</v>
       </c>
       <c r="G18" t="n">
-        <v>2.9587</v>
+        <v>1.305</v>
       </c>
       <c r="H18" t="b">
         <v>0</v>
@@ -6519,16 +6519,16 @@
         <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>1.091</v>
+        <v>0.8144</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9</v>
+        <v>0.4441</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.9405</v>
+        <v>-0.4417</v>
       </c>
       <c r="G19" t="n">
-        <v>4.1226</v>
+        <v>2.0705</v>
       </c>
       <c r="H19" t="b">
         <v>0</v>
@@ -6545,16 +6545,16 @@
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>1.4369</v>
+        <v>0.6727</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6109</v>
+        <v>0.4788</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.1394</v>
+        <v>-0.3947</v>
       </c>
       <c r="G20" t="n">
-        <v>4.0132</v>
+        <v>1.7402</v>
       </c>
       <c r="H20" t="b">
         <v>0</v>
@@ -6571,16 +6571,16 @@
         <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>0.8055</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="E21" t="n">
         <v>0.9</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.0527</v>
+        <v>-1.1075</v>
       </c>
       <c r="G21" t="n">
-        <v>3.6636</v>
+        <v>1.261</v>
       </c>
       <c r="H21" t="b">
         <v>0</v>
@@ -6597,16 +6597,16 @@
         <v>7</v>
       </c>
       <c r="D22" t="n">
-        <v>1.0734</v>
+        <v>0.9006</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9</v>
+        <v>0.2055</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.6631</v>
+        <v>-0.2332</v>
       </c>
       <c r="G22" t="n">
-        <v>3.8098</v>
+        <v>2.0344</v>
       </c>
       <c r="H22" t="b">
         <v>0</v>
@@ -6623,16 +6623,16 @@
         <v>8</v>
       </c>
       <c r="D23" t="n">
-        <v>0.7481</v>
+        <v>0.5764</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9</v>
+        <v>0.6688</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.8981</v>
+        <v>-0.52</v>
       </c>
       <c r="G23" t="n">
-        <v>3.3942</v>
+        <v>1.6728</v>
       </c>
       <c r="H23" t="b">
         <v>0</v>
@@ -6649,16 +6649,16 @@
         <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>0.3458</v>
+        <v>-0.1417</v>
       </c>
       <c r="E24" t="n">
         <v>0.9</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.4215</v>
+        <v>-1.2883</v>
       </c>
       <c r="G24" t="n">
-        <v>3.1132</v>
+        <v>1.005</v>
       </c>
       <c r="H24" t="b">
         <v>0</v>
@@ -6675,16 +6675,16 @@
         <v>6</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.2856</v>
+        <v>-0.7376</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9</v>
+        <v>0.5574</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.3171</v>
+        <v>-1.9937</v>
       </c>
       <c r="G25" t="n">
-        <v>2.7459</v>
+        <v>0.5184</v>
       </c>
       <c r="H25" t="b">
         <v>0</v>
@@ -6701,16 +6701,16 @@
         <v>7</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.0177</v>
+        <v>0.0862</v>
       </c>
       <c r="E26" t="n">
         <v>0.9</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.9348</v>
+        <v>-1.1225</v>
       </c>
       <c r="G26" t="n">
-        <v>2.8994</v>
+        <v>1.2948</v>
       </c>
       <c r="H26" t="b">
         <v>0</v>
@@ -6727,16 +6727,16 @@
         <v>8</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.343</v>
+        <v>-0.238</v>
       </c>
       <c r="E27" t="n">
         <v>0.9</v>
       </c>
       <c r="F27" t="n">
-        <v>-3.1755</v>
+        <v>-1.4116</v>
       </c>
       <c r="G27" t="n">
-        <v>2.4895</v>
+        <v>0.9356</v>
       </c>
       <c r="H27" t="b">
         <v>0</v>
@@ -6753,16 +6753,16 @@
         <v>6</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6314</v>
+        <v>-0.596</v>
       </c>
       <c r="E28" t="n">
-        <v>0.9</v>
+        <v>0.6098</v>
       </c>
       <c r="F28" t="n">
-        <v>-3.2077</v>
+        <v>-1.6634</v>
       </c>
       <c r="G28" t="n">
-        <v>1.9449</v>
+        <v>0.4715</v>
       </c>
       <c r="H28" t="b">
         <v>0</v>
@@ -6779,16 +6779,16 @@
         <v>7</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.3635</v>
+        <v>0.2278</v>
       </c>
       <c r="E29" t="n">
         <v>0.9</v>
       </c>
       <c r="F29" t="n">
-        <v>-2.8041</v>
+        <v>-0.7834</v>
       </c>
       <c r="G29" t="n">
-        <v>2.0771</v>
+        <v>1.2391</v>
       </c>
       <c r="H29" t="b">
         <v>0</v>
@@ -6805,16 +6805,16 @@
         <v>8</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6888</v>
+        <v>-0.0963</v>
       </c>
       <c r="E30" t="n">
         <v>0.9</v>
       </c>
       <c r="F30" t="n">
-        <v>-3.0277</v>
+        <v>-1.0654</v>
       </c>
       <c r="G30" t="n">
-        <v>1.65</v>
+        <v>0.8728</v>
       </c>
       <c r="H30" t="b">
         <v>0</v>
@@ -6831,16 +6831,16 @@
         <v>7</v>
       </c>
       <c r="D31" t="n">
-        <v>0.2679</v>
+        <v>0.8238</v>
       </c>
       <c r="E31" t="n">
-        <v>0.9</v>
+        <v>0.3018</v>
       </c>
       <c r="F31" t="n">
-        <v>-2.4686</v>
+        <v>-0.31</v>
       </c>
       <c r="G31" t="n">
-        <v>3.0043</v>
+        <v>1.9576</v>
       </c>
       <c r="H31" t="b">
         <v>0</v>
@@ -6857,16 +6857,16 @@
         <v>8</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.0574</v>
+        <v>0.4997</v>
       </c>
       <c r="E32" t="n">
-        <v>0.9</v>
+        <v>0.7956</v>
       </c>
       <c r="F32" t="n">
-        <v>-2.7035</v>
+        <v>-0.5967</v>
       </c>
       <c r="G32" t="n">
-        <v>2.5887</v>
+        <v>1.5961</v>
       </c>
       <c r="H32" t="b">
         <v>0</v>
@@ -6883,16 +6883,16 @@
         <v>8</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.3253</v>
+        <v>-0.3241</v>
       </c>
       <c r="E33" t="n">
         <v>0.9</v>
       </c>
       <c r="F33" t="n">
-        <v>-2.8395</v>
+        <v>-1.3659</v>
       </c>
       <c r="G33" t="n">
-        <v>2.1889</v>
+        <v>0.7176</v>
       </c>
       <c r="H33" t="b">
         <v>0</v>
@@ -6964,16 +6964,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.6145</v>
+        <v>-0.6085</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7412</v>
+        <v>0.3563</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.968</v>
+        <v>-1.9256</v>
       </c>
       <c r="G2" t="n">
-        <v>4.197</v>
+        <v>0.7086</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
@@ -6994,16 +6994,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3.2321</v>
+        <v>0.3578</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0692</v>
+        <v>0.604</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2665</v>
+        <v>-0.9893999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>6.7308</v>
+        <v>1.705</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
@@ -7024,16 +7024,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-1.9568</v>
+        <v>0.2373</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2668</v>
+        <v>0.7292</v>
       </c>
       <c r="F4" t="n">
-        <v>-5.4673</v>
+        <v>-1.0829</v>
       </c>
       <c r="G4" t="n">
-        <v>1.5538</v>
+        <v>1.5576</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
@@ -7054,16 +7054,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.625</v>
+        <v>0.2974</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3608</v>
+        <v>0.6647</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.926</v>
+        <v>-1.0303</v>
       </c>
       <c r="G5" t="n">
-        <v>5.1759</v>
+        <v>1.6251</v>
       </c>
       <c r="H5" t="b">
         <v>0</v>
@@ -7080,16 +7080,16 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>-5.1408</v>
+        <v>1.3659</v>
       </c>
       <c r="E6" t="n">
         <v>0.9</v>
       </c>
       <c r="F6" t="n">
-        <v>-18.1211</v>
+        <v>-3.557</v>
       </c>
       <c r="G6" t="n">
-        <v>7.8396</v>
+        <v>6.2889</v>
       </c>
       <c r="H6" t="b">
         <v>0</v>
@@ -7106,16 +7106,16 @@
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>-8.346500000000001</v>
+        <v>-1.0597</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2769</v>
+        <v>0.9</v>
       </c>
       <c r="F7" t="n">
-        <v>-19.5878</v>
+        <v>-5.323</v>
       </c>
       <c r="G7" t="n">
-        <v>2.8948</v>
+        <v>3.2037</v>
       </c>
       <c r="H7" t="b">
         <v>0</v>
@@ -7132,16 +7132,16 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>-5.8976</v>
+        <v>0.3651</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7252</v>
+        <v>0.9</v>
       </c>
       <c r="F8" t="n">
-        <v>-17.8208</v>
+        <v>-4.1569</v>
       </c>
       <c r="G8" t="n">
-        <v>6.0256</v>
+        <v>4.8871</v>
       </c>
       <c r="H8" t="b">
         <v>0</v>
@@ -7158,16 +7158,16 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>-7.3648</v>
+        <v>-0.4905</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3014</v>
+        <v>0.9</v>
       </c>
       <c r="F9" t="n">
-        <v>-17.4975</v>
+        <v>-4.3335</v>
       </c>
       <c r="G9" t="n">
-        <v>2.768</v>
+        <v>3.3525</v>
       </c>
       <c r="H9" t="b">
         <v>0</v>
@@ -7184,16 +7184,16 @@
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>-9.084</v>
+        <v>-1.3894</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1889</v>
+        <v>0.9</v>
       </c>
       <c r="F10" t="n">
-        <v>-20.3253</v>
+        <v>-5.6527</v>
       </c>
       <c r="G10" t="n">
-        <v>2.1573</v>
+        <v>2.874</v>
       </c>
       <c r="H10" t="b">
         <v>0</v>
@@ -7210,16 +7210,16 @@
         <v>7</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.1689</v>
+        <v>1.2583</v>
       </c>
       <c r="E11" t="n">
-        <v>0.4099</v>
+        <v>0.9</v>
       </c>
       <c r="F11" t="n">
-        <v>-17.9316</v>
+        <v>-2.8236</v>
       </c>
       <c r="G11" t="n">
-        <v>3.5938</v>
+        <v>5.3402</v>
       </c>
       <c r="H11" t="b">
         <v>0</v>
@@ -7236,16 +7236,16 @@
         <v>8</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.5966</v>
+        <v>-0.798</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1693</v>
+        <v>0.9</v>
       </c>
       <c r="F12" t="n">
-        <v>-19.004</v>
+        <v>-4.7451</v>
       </c>
       <c r="G12" t="n">
-        <v>1.8108</v>
+        <v>3.1492</v>
       </c>
       <c r="H12" t="b">
         <v>0</v>
@@ -7262,16 +7262,16 @@
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.2057</v>
+        <v>-2.4256</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9</v>
+        <v>0.7287</v>
       </c>
       <c r="F13" t="n">
-        <v>-16.186</v>
+        <v>-7.3485</v>
       </c>
       <c r="G13" t="n">
-        <v>9.7746</v>
+        <v>2.4973</v>
       </c>
       <c r="H13" t="b">
         <v>0</v>
@@ -7288,16 +7288,16 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.7568</v>
+        <v>-1.0009</v>
       </c>
       <c r="E14" t="n">
         <v>0.9</v>
       </c>
       <c r="F14" t="n">
-        <v>-14.332</v>
+        <v>-6.1494</v>
       </c>
       <c r="G14" t="n">
-        <v>12.8183</v>
+        <v>4.1477</v>
       </c>
       <c r="H14" t="b">
         <v>0</v>
@@ -7314,16 +7314,16 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>-2.224</v>
+        <v>-1.8564</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9</v>
+        <v>0.8843</v>
       </c>
       <c r="F15" t="n">
-        <v>-14.2571</v>
+        <v>-6.4201</v>
       </c>
       <c r="G15" t="n">
-        <v>9.809100000000001</v>
+        <v>2.7072</v>
       </c>
       <c r="H15" t="b">
         <v>0</v>
@@ -7340,16 +7340,16 @@
         <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>-3.9432</v>
+        <v>-2.7553</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9</v>
+        <v>0.6073</v>
       </c>
       <c r="F16" t="n">
-        <v>-16.9236</v>
+        <v>-7.6782</v>
       </c>
       <c r="G16" t="n">
-        <v>9.037100000000001</v>
+        <v>2.1676</v>
       </c>
       <c r="H16" t="b">
         <v>0</v>
@@ -7366,16 +7366,16 @@
         <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.0282</v>
+        <v>-0.1076</v>
       </c>
       <c r="E17" t="n">
         <v>0.9</v>
       </c>
       <c r="F17" t="n">
-        <v>-14.5963</v>
+        <v>-4.8742</v>
       </c>
       <c r="G17" t="n">
-        <v>10.54</v>
+        <v>4.659</v>
       </c>
       <c r="H17" t="b">
         <v>0</v>
@@ -7392,16 +7392,16 @@
         <v>8</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.4558</v>
+        <v>-2.1639</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9</v>
+        <v>0.7785</v>
       </c>
       <c r="F18" t="n">
-        <v>-15.7211</v>
+        <v>-6.8156</v>
       </c>
       <c r="G18" t="n">
-        <v>8.8094</v>
+        <v>2.4878</v>
       </c>
       <c r="H18" t="b">
         <v>0</v>
@@ -7418,16 +7418,16 @@
         <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>2.4489</v>
+        <v>1.4247</v>
       </c>
       <c r="E19" t="n">
         <v>0.9</v>
       </c>
       <c r="F19" t="n">
-        <v>-9.474299999999999</v>
+        <v>-3.0973</v>
       </c>
       <c r="G19" t="n">
-        <v>14.3721</v>
+        <v>5.9467</v>
       </c>
       <c r="H19" t="b">
         <v>0</v>
@@ -7444,16 +7444,16 @@
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9817</v>
+        <v>0.5692</v>
       </c>
       <c r="E20" t="n">
         <v>0.9</v>
       </c>
       <c r="F20" t="n">
-        <v>-9.1511</v>
+        <v>-3.2738</v>
       </c>
       <c r="G20" t="n">
-        <v>11.1145</v>
+        <v>4.4121</v>
       </c>
       <c r="H20" t="b">
         <v>0</v>
@@ -7470,16 +7470,16 @@
         <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.7375</v>
+        <v>-0.3297</v>
       </c>
       <c r="E21" t="n">
         <v>0.9</v>
       </c>
       <c r="F21" t="n">
-        <v>-11.9788</v>
+        <v>-4.5931</v>
       </c>
       <c r="G21" t="n">
-        <v>10.5038</v>
+        <v>3.9337</v>
       </c>
       <c r="H21" t="b">
         <v>0</v>
@@ -7496,16 +7496,16 @@
         <v>7</v>
       </c>
       <c r="D22" t="n">
-        <v>1.1776</v>
+        <v>2.318</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9</v>
+        <v>0.5925</v>
       </c>
       <c r="F22" t="n">
-        <v>-9.5852</v>
+        <v>-1.7639</v>
       </c>
       <c r="G22" t="n">
-        <v>11.9403</v>
+        <v>6.3998</v>
       </c>
       <c r="H22" t="b">
         <v>0</v>
@@ -7522,16 +7522,16 @@
         <v>8</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2501</v>
+        <v>0.2617</v>
       </c>
       <c r="E23" t="n">
         <v>0.9</v>
       </c>
       <c r="F23" t="n">
-        <v>-10.6575</v>
+        <v>-3.6854</v>
       </c>
       <c r="G23" t="n">
-        <v>10.1573</v>
+        <v>4.2088</v>
       </c>
       <c r="H23" t="b">
         <v>0</v>
@@ -7548,16 +7548,16 @@
         <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.4672</v>
+        <v>-0.8556</v>
       </c>
       <c r="E24" t="n">
         <v>0.9</v>
       </c>
       <c r="F24" t="n">
-        <v>-12.3515</v>
+        <v>-4.9836</v>
       </c>
       <c r="G24" t="n">
-        <v>9.4171</v>
+        <v>3.2724</v>
       </c>
       <c r="H24" t="b">
         <v>0</v>
@@ -7574,16 +7574,16 @@
         <v>6</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.1864</v>
+        <v>-1.7544</v>
       </c>
       <c r="E25" t="n">
         <v>0.9</v>
       </c>
       <c r="F25" t="n">
-        <v>-15.1096</v>
+        <v>-6.2764</v>
       </c>
       <c r="G25" t="n">
-        <v>8.736800000000001</v>
+        <v>2.7676</v>
       </c>
       <c r="H25" t="b">
         <v>0</v>
@@ -7600,16 +7600,16 @@
         <v>7</v>
       </c>
       <c r="D26" t="n">
-        <v>-1.2713</v>
+        <v>0.8932</v>
       </c>
       <c r="E26" t="n">
         <v>0.9</v>
       </c>
       <c r="F26" t="n">
-        <v>-12.7444</v>
+        <v>-3.4581</v>
       </c>
       <c r="G26" t="n">
-        <v>10.2017</v>
+        <v>5.2445</v>
       </c>
       <c r="H26" t="b">
         <v>0</v>
@@ -7626,16 +7626,16 @@
         <v>8</v>
       </c>
       <c r="D27" t="n">
-        <v>-2.699</v>
+        <v>-1.163</v>
       </c>
       <c r="E27" t="n">
         <v>0.9</v>
       </c>
       <c r="F27" t="n">
-        <v>-13.8395</v>
+        <v>-5.3882</v>
       </c>
       <c r="G27" t="n">
-        <v>8.4415</v>
+        <v>3.0621</v>
       </c>
       <c r="H27" t="b">
         <v>0</v>
@@ -7652,16 +7652,16 @@
         <v>6</v>
       </c>
       <c r="D28" t="n">
-        <v>-1.7192</v>
+        <v>-0.8989</v>
       </c>
       <c r="E28" t="n">
         <v>0.9</v>
       </c>
       <c r="F28" t="n">
-        <v>-11.852</v>
+        <v>-4.7418</v>
       </c>
       <c r="G28" t="n">
-        <v>8.413500000000001</v>
+        <v>2.9441</v>
       </c>
       <c r="H28" t="b">
         <v>0</v>
@@ -7678,16 +7678,16 @@
         <v>7</v>
       </c>
       <c r="D29" t="n">
-        <v>0.1959</v>
+        <v>1.7488</v>
       </c>
       <c r="E29" t="n">
-        <v>0.9</v>
+        <v>0.751</v>
       </c>
       <c r="F29" t="n">
-        <v>-9.4032</v>
+        <v>-1.8918</v>
       </c>
       <c r="G29" t="n">
-        <v>9.7949</v>
+        <v>5.3894</v>
       </c>
       <c r="H29" t="b">
         <v>0</v>
@@ -7704,16 +7704,16 @@
         <v>8</v>
       </c>
       <c r="D30" t="n">
-        <v>-1.2318</v>
+        <v>-0.3075</v>
       </c>
       <c r="E30" t="n">
         <v>0.9</v>
       </c>
       <c r="F30" t="n">
-        <v>-10.4307</v>
+        <v>-3.7963</v>
       </c>
       <c r="G30" t="n">
-        <v>7.9671</v>
+        <v>3.1813</v>
       </c>
       <c r="H30" t="b">
         <v>0</v>
@@ -7730,16 +7730,16 @@
         <v>7</v>
       </c>
       <c r="D31" t="n">
-        <v>1.9151</v>
+        <v>2.6477</v>
       </c>
       <c r="E31" t="n">
-        <v>0.9</v>
+        <v>0.4436</v>
       </c>
       <c r="F31" t="n">
-        <v>-8.8476</v>
+        <v>-1.4342</v>
       </c>
       <c r="G31" t="n">
-        <v>12.6778</v>
+        <v>6.7295</v>
       </c>
       <c r="H31" t="b">
         <v>0</v>
@@ -7756,16 +7756,16 @@
         <v>8</v>
       </c>
       <c r="D32" t="n">
-        <v>0.4874</v>
+        <v>0.5914</v>
       </c>
       <c r="E32" t="n">
         <v>0.9</v>
       </c>
       <c r="F32" t="n">
-        <v>-9.92</v>
+        <v>-3.3557</v>
       </c>
       <c r="G32" t="n">
-        <v>10.8948</v>
+        <v>4.5385</v>
       </c>
       <c r="H32" t="b">
         <v>0</v>
@@ -7782,16 +7782,16 @@
         <v>8</v>
       </c>
       <c r="D33" t="n">
-        <v>-1.4277</v>
+        <v>-2.0563</v>
       </c>
       <c r="E33" t="n">
-        <v>0.9</v>
+        <v>0.628</v>
       </c>
       <c r="F33" t="n">
-        <v>-11.3162</v>
+        <v>-5.8066</v>
       </c>
       <c r="G33" t="n">
-        <v>8.460900000000001</v>
+        <v>1.6941</v>
       </c>
       <c r="H33" t="b">
         <v>0</v>
@@ -7863,16 +7863,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-3.349</v>
+        <v>5.8003</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7317</v>
+        <v>0.5770999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>-22.1583</v>
+        <v>-14.6151</v>
       </c>
       <c r="G2" t="n">
-        <v>15.4603</v>
+        <v>26.2157</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
@@ -7893,16 +7893,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-1.1159</v>
+        <v>6.7758</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9</v>
+        <v>0.5143</v>
       </c>
       <c r="F3" t="n">
-        <v>-20.2477</v>
+        <v>-13.9335</v>
       </c>
       <c r="G3" t="n">
-        <v>18.0158</v>
+        <v>27.4851</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
@@ -7923,16 +7923,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.8519</v>
+        <v>12.0127</v>
       </c>
       <c r="E4" t="n">
-        <v>0.065</v>
+        <v>0.2323</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.0937</v>
+        <v>-7.9954</v>
       </c>
       <c r="G4" t="n">
-        <v>34.7976</v>
+        <v>32.0208</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
@@ -7953,16 +7953,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-11.5845</v>
+        <v>-11.8941</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2127</v>
+        <v>0.2401</v>
       </c>
       <c r="F5" t="n">
-        <v>-30.0658</v>
+        <v>-32.0451</v>
       </c>
       <c r="G5" t="n">
-        <v>6.8967</v>
+        <v>8.2569</v>
       </c>
       <c r="H5" t="b">
         <v>0</v>
@@ -7979,16 +7979,16 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>20.9447</v>
+        <v>20.3219</v>
       </c>
       <c r="E6" t="n">
         <v>0.9</v>
       </c>
       <c r="F6" t="n">
-        <v>-47.142</v>
+        <v>-54.2905</v>
       </c>
       <c r="G6" t="n">
-        <v>89.0314</v>
+        <v>94.9342</v>
       </c>
       <c r="H6" t="b">
         <v>0</v>
@@ -8005,16 +8005,16 @@
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>44.3255</v>
+        <v>38.1316</v>
       </c>
       <c r="E7" t="n">
-        <v>0.263</v>
+        <v>0.5522</v>
       </c>
       <c r="F7" t="n">
-        <v>-14.6393</v>
+        <v>-26.4845</v>
       </c>
       <c r="G7" t="n">
-        <v>103.2904</v>
+        <v>102.7478</v>
       </c>
       <c r="H7" t="b">
         <v>0</v>
@@ -8031,16 +8031,16 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>19.6809</v>
+        <v>18.6836</v>
       </c>
       <c r="E8" t="n">
         <v>0.9</v>
       </c>
       <c r="F8" t="n">
-        <v>-42.8607</v>
+        <v>-49.8522</v>
       </c>
       <c r="G8" t="n">
-        <v>82.2225</v>
+        <v>87.21939999999999</v>
       </c>
       <c r="H8" t="b">
         <v>0</v>
@@ -8057,16 +8057,16 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>6.1002</v>
+        <v>-6.1427</v>
       </c>
       <c r="E9" t="n">
         <v>0.9</v>
       </c>
       <c r="F9" t="n">
-        <v>-47.05</v>
+        <v>-64.387</v>
       </c>
       <c r="G9" t="n">
-        <v>59.2504</v>
+        <v>52.1015</v>
       </c>
       <c r="H9" t="b">
         <v>0</v>
@@ -8083,16 +8083,16 @@
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>34.0229</v>
+        <v>35.2443</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5759</v>
+        <v>0.6331</v>
       </c>
       <c r="F10" t="n">
-        <v>-24.9419</v>
+        <v>-29.3719</v>
       </c>
       <c r="G10" t="n">
-        <v>92.98779999999999</v>
+        <v>99.8605</v>
       </c>
       <c r="H10" t="b">
         <v>0</v>
@@ -8109,16 +8109,16 @@
         <v>7</v>
       </c>
       <c r="D11" t="n">
-        <v>22.6079</v>
+        <v>15.7941</v>
       </c>
       <c r="E11" t="n">
-        <v>0.8958</v>
+        <v>0.9</v>
       </c>
       <c r="F11" t="n">
-        <v>-33.8466</v>
+        <v>-46.0711</v>
       </c>
       <c r="G11" t="n">
-        <v>79.0624</v>
+        <v>77.65940000000001</v>
       </c>
       <c r="H11" t="b">
         <v>0</v>
@@ -8135,16 +8135,16 @@
         <v>8</v>
       </c>
       <c r="D12" t="n">
-        <v>32.8444</v>
+        <v>14.446</v>
       </c>
       <c r="E12" t="n">
-        <v>0.5313</v>
+        <v>0.9</v>
       </c>
       <c r="F12" t="n">
-        <v>-21.7464</v>
+        <v>-45.377</v>
       </c>
       <c r="G12" t="n">
-        <v>87.43519999999999</v>
+        <v>74.2689</v>
       </c>
       <c r="H12" t="b">
         <v>0</v>
@@ -8161,16 +8161,16 @@
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>23.3808</v>
+        <v>17.8098</v>
       </c>
       <c r="E13" t="n">
         <v>0.9</v>
       </c>
       <c r="F13" t="n">
-        <v>-44.7059</v>
+        <v>-56.8026</v>
       </c>
       <c r="G13" t="n">
-        <v>91.4675</v>
+        <v>92.4221</v>
       </c>
       <c r="H13" t="b">
         <v>0</v>
@@ -8187,16 +8187,16 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.2638</v>
+        <v>-1.6382</v>
       </c>
       <c r="E14" t="n">
         <v>0.9</v>
       </c>
       <c r="F14" t="n">
-        <v>-72.4706</v>
+        <v>-79.66970000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>69.943</v>
+        <v>76.39319999999999</v>
       </c>
       <c r="H14" t="b">
         <v>0</v>
@@ -8213,16 +8213,16 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>-14.8445</v>
+        <v>-26.4646</v>
       </c>
       <c r="E15" t="n">
         <v>0.9</v>
       </c>
       <c r="F15" t="n">
-        <v>-77.96259999999999</v>
+        <v>-95.63209999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>48.2735</v>
+        <v>42.7029</v>
       </c>
       <c r="H15" t="b">
         <v>0</v>
@@ -8239,16 +8239,16 @@
         <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>13.0782</v>
+        <v>14.9224</v>
       </c>
       <c r="E16" t="n">
         <v>0.9</v>
       </c>
       <c r="F16" t="n">
-        <v>-55.0085</v>
+        <v>-59.6899</v>
       </c>
       <c r="G16" t="n">
-        <v>81.1649</v>
+        <v>89.5348</v>
       </c>
       <c r="H16" t="b">
         <v>0</v>
@@ -8265,16 +8265,16 @@
         <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>1.6632</v>
+        <v>-4.5277</v>
       </c>
       <c r="E17" t="n">
         <v>0.9</v>
       </c>
       <c r="F17" t="n">
-        <v>-64.2615</v>
+        <v>-76.77079999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>67.5879</v>
+        <v>67.7154</v>
       </c>
       <c r="H17" t="b">
         <v>0</v>
@@ -8291,16 +8291,16 @@
         <v>8</v>
       </c>
       <c r="D18" t="n">
-        <v>11.8997</v>
+        <v>-5.8759</v>
       </c>
       <c r="E18" t="n">
         <v>0.9</v>
       </c>
       <c r="F18" t="n">
-        <v>-52.4362</v>
+        <v>-76.3779</v>
       </c>
       <c r="G18" t="n">
-        <v>76.23560000000001</v>
+        <v>64.62609999999999</v>
       </c>
       <c r="H18" t="b">
         <v>0</v>
@@ -8317,16 +8317,16 @@
         <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>-24.6446</v>
+        <v>-19.448</v>
       </c>
       <c r="E19" t="n">
         <v>0.9</v>
       </c>
       <c r="F19" t="n">
-        <v>-87.1863</v>
+        <v>-87.9838</v>
       </c>
       <c r="G19" t="n">
-        <v>37.897</v>
+        <v>49.0878</v>
       </c>
       <c r="H19" t="b">
         <v>0</v>
@@ -8343,16 +8343,16 @@
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>-38.2254</v>
+        <v>-44.2744</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3137</v>
+        <v>0.2508</v>
       </c>
       <c r="F20" t="n">
-        <v>-91.3755</v>
+        <v>-102.5186</v>
       </c>
       <c r="G20" t="n">
-        <v>14.9248</v>
+        <v>13.9699</v>
       </c>
       <c r="H20" t="b">
         <v>0</v>
@@ -8369,16 +8369,16 @@
         <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>-10.3026</v>
+        <v>-2.8873</v>
       </c>
       <c r="E21" t="n">
         <v>0.9</v>
       </c>
       <c r="F21" t="n">
-        <v>-69.26739999999999</v>
+        <v>-67.5035</v>
       </c>
       <c r="G21" t="n">
-        <v>48.6622</v>
+        <v>61.7288</v>
       </c>
       <c r="H21" t="b">
         <v>0</v>
@@ -8395,16 +8395,16 @@
         <v>7</v>
       </c>
       <c r="D22" t="n">
-        <v>-21.7176</v>
+        <v>-22.3375</v>
       </c>
       <c r="E22" t="n">
         <v>0.9</v>
       </c>
       <c r="F22" t="n">
-        <v>-78.1721</v>
+        <v>-84.2028</v>
       </c>
       <c r="G22" t="n">
-        <v>34.7369</v>
+        <v>39.5278</v>
       </c>
       <c r="H22" t="b">
         <v>0</v>
@@ -8421,16 +8421,16 @@
         <v>8</v>
       </c>
       <c r="D23" t="n">
-        <v>-11.4811</v>
+        <v>-23.6857</v>
       </c>
       <c r="E23" t="n">
         <v>0.9</v>
       </c>
       <c r="F23" t="n">
-        <v>-66.0719</v>
+        <v>-83.5086</v>
       </c>
       <c r="G23" t="n">
-        <v>43.1097</v>
+        <v>36.1373</v>
       </c>
       <c r="H23" t="b">
         <v>0</v>
@@ -8447,16 +8447,16 @@
         <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>-13.5807</v>
+        <v>-24.8264</v>
       </c>
       <c r="E24" t="n">
         <v>0.9</v>
       </c>
       <c r="F24" t="n">
-        <v>-70.67310000000001</v>
+        <v>-87.3907</v>
       </c>
       <c r="G24" t="n">
-        <v>43.5117</v>
+        <v>37.738</v>
       </c>
       <c r="H24" t="b">
         <v>0</v>
@@ -8473,16 +8473,16 @@
         <v>6</v>
       </c>
       <c r="D25" t="n">
-        <v>14.342</v>
+        <v>16.5607</v>
       </c>
       <c r="E25" t="n">
         <v>0.9</v>
       </c>
       <c r="F25" t="n">
-        <v>-48.1996</v>
+        <v>-51.9751</v>
       </c>
       <c r="G25" t="n">
-        <v>76.8837</v>
+        <v>85.09650000000001</v>
       </c>
       <c r="H25" t="b">
         <v>0</v>
@@ -8499,16 +8499,16 @@
         <v>7</v>
       </c>
       <c r="D26" t="n">
-        <v>2.927</v>
+        <v>-2.8895</v>
       </c>
       <c r="E26" t="n">
         <v>0.9</v>
       </c>
       <c r="F26" t="n">
-        <v>-57.2537</v>
+        <v>-68.8381</v>
       </c>
       <c r="G26" t="n">
-        <v>63.1077</v>
+        <v>63.0591</v>
       </c>
       <c r="H26" t="b">
         <v>0</v>
@@ -8525,16 +8525,16 @@
         <v>8</v>
       </c>
       <c r="D27" t="n">
-        <v>13.1635</v>
+        <v>-4.2377</v>
       </c>
       <c r="E27" t="n">
         <v>0.9</v>
       </c>
       <c r="F27" t="n">
-        <v>-45.2724</v>
+        <v>-68.2743</v>
       </c>
       <c r="G27" t="n">
-        <v>71.59950000000001</v>
+        <v>59.799</v>
       </c>
       <c r="H27" t="b">
         <v>0</v>
@@ -8551,16 +8551,16 @@
         <v>6</v>
       </c>
       <c r="D28" t="n">
-        <v>27.9227</v>
+        <v>41.387</v>
       </c>
       <c r="E28" t="n">
-        <v>0.6695</v>
+        <v>0.3279</v>
       </c>
       <c r="F28" t="n">
-        <v>-25.2274</v>
+        <v>-16.8572</v>
       </c>
       <c r="G28" t="n">
-        <v>81.0729</v>
+        <v>99.6313</v>
       </c>
       <c r="H28" t="b">
         <v>0</v>
@@ -8577,16 +8577,16 @@
         <v>7</v>
       </c>
       <c r="D29" t="n">
-        <v>16.5077</v>
+        <v>21.9369</v>
       </c>
       <c r="E29" t="n">
         <v>0.9</v>
       </c>
       <c r="F29" t="n">
-        <v>-33.8431</v>
+        <v>-33.2397</v>
       </c>
       <c r="G29" t="n">
-        <v>66.85850000000001</v>
+        <v>77.1134</v>
       </c>
       <c r="H29" t="b">
         <v>0</v>
@@ -8603,16 +8603,16 @@
         <v>8</v>
       </c>
       <c r="D30" t="n">
-        <v>26.7442</v>
+        <v>20.5887</v>
       </c>
       <c r="E30" t="n">
-        <v>0.6171</v>
+        <v>0.9</v>
       </c>
       <c r="F30" t="n">
-        <v>-21.5077</v>
+        <v>-32.2878</v>
       </c>
       <c r="G30" t="n">
-        <v>74.9962</v>
+        <v>73.4652</v>
       </c>
       <c r="H30" t="b">
         <v>0</v>
@@ -8629,16 +8629,16 @@
         <v>7</v>
       </c>
       <c r="D31" t="n">
-        <v>-11.415</v>
+        <v>-19.4502</v>
       </c>
       <c r="E31" t="n">
         <v>0.9</v>
       </c>
       <c r="F31" t="n">
-        <v>-67.8695</v>
+        <v>-81.3154</v>
       </c>
       <c r="G31" t="n">
-        <v>45.0395</v>
+        <v>42.4151</v>
       </c>
       <c r="H31" t="b">
         <v>0</v>
@@ -8655,16 +8655,16 @@
         <v>8</v>
       </c>
       <c r="D32" t="n">
-        <v>-1.1785</v>
+        <v>-20.7983</v>
       </c>
       <c r="E32" t="n">
         <v>0.9</v>
       </c>
       <c r="F32" t="n">
-        <v>-55.7693</v>
+        <v>-80.62130000000001</v>
       </c>
       <c r="G32" t="n">
-        <v>53.4123</v>
+        <v>39.0246</v>
       </c>
       <c r="H32" t="b">
         <v>0</v>
@@ -8681,16 +8681,16 @@
         <v>8</v>
       </c>
       <c r="D33" t="n">
-        <v>10.2365</v>
+        <v>-1.3482</v>
       </c>
       <c r="E33" t="n">
         <v>0.9</v>
       </c>
       <c r="F33" t="n">
-        <v>-41.6327</v>
+        <v>-58.1887</v>
       </c>
       <c r="G33" t="n">
-        <v>62.1058</v>
+        <v>55.4924</v>
       </c>
       <c r="H33" t="b">
         <v>0</v>
@@ -8762,16 +8762,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.0317</v>
+        <v>-0.0289</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7955</v>
+        <v>0.7922</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2056</v>
+        <v>-0.2417</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2689</v>
+        <v>0.184</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
@@ -8792,16 +8792,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.07489999999999999</v>
+        <v>0.1649</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9</v>
+        <v>0.6123</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.5631</v>
+        <v>-0.2666</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4133</v>
+        <v>0.5964</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
@@ -8822,16 +8822,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.07480000000000001</v>
+        <v>0.2134</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8945</v>
+        <v>0.3347</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3383</v>
+        <v>-0.1517</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4879</v>
+        <v>0.5785</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
@@ -8852,16 +8852,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.1497</v>
+        <v>0.0485</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5681</v>
+        <v>0.9</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2122</v>
+        <v>-0.2713</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5115</v>
+        <v>0.3683</v>
       </c>
       <c r="H5" t="b">
         <v>0</v>
@@ -8882,16 +8882,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.1579</v>
+        <v>0.117</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1727</v>
+        <v>0.2623</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0727</v>
+        <v>-0.0919</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3885</v>
+        <v>0.3259</v>
       </c>
       <c r="H6" t="b">
         <v>0</v>
@@ -8912,16 +8912,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.0387</v>
+        <v>0.027</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7582</v>
+        <v>0.8103</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2048</v>
+        <v>-0.1917</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2822</v>
+        <v>0.2456</v>
       </c>
       <c r="H7" t="b">
         <v>0</v>
@@ -8938,16 +8938,16 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3364</v>
+        <v>0.2538</v>
       </c>
       <c r="E8" t="n">
-        <v>0.644</v>
+        <v>0.8233</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3</v>
+        <v>-0.3368</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9729</v>
+        <v>0.8444</v>
       </c>
       <c r="H8" t="b">
         <v>0</v>
@@ -8964,16 +8964,16 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>0.425</v>
+        <v>0.5003</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4704</v>
+        <v>0.1994</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2561</v>
+        <v>-0.1318</v>
       </c>
       <c r="G9" t="n">
-        <v>1.1061</v>
+        <v>1.1324</v>
       </c>
       <c r="H9" t="b">
         <v>0</v>
@@ -8990,16 +8990,16 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3858</v>
+        <v>0.3446</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5354</v>
+        <v>0.5754</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2696</v>
+        <v>-0.2637</v>
       </c>
       <c r="G10" t="n">
-        <v>1.0412</v>
+        <v>0.9528</v>
       </c>
       <c r="H10" t="b">
         <v>0</v>
@@ -9016,16 +9016,16 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6183999999999999</v>
+        <v>0.3892</v>
       </c>
       <c r="E11" t="n">
-        <v>0.3241</v>
+        <v>0.7378</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.261</v>
+        <v>-0.4268</v>
       </c>
       <c r="G11" t="n">
-        <v>1.4977</v>
+        <v>1.2052</v>
       </c>
       <c r="H11" t="b">
         <v>0</v>
@@ -9042,16 +9042,16 @@
         <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.0245</v>
+        <v>0.1802</v>
       </c>
       <c r="E12" t="n">
         <v>0.9</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.7056</v>
+        <v>-0.4519</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6566</v>
+        <v>0.8123</v>
       </c>
       <c r="H12" t="b">
         <v>0</v>
@@ -9068,16 +9068,16 @@
         <v>7</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2103</v>
+        <v>0.0742</v>
       </c>
       <c r="E13" t="n">
         <v>0.9</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.6691</v>
+        <v>-0.7418</v>
       </c>
       <c r="G13" t="n">
-        <v>1.0896</v>
+        <v>0.8902</v>
       </c>
       <c r="H13" t="b">
         <v>0</v>
@@ -9094,16 +9094,16 @@
         <v>8</v>
       </c>
       <c r="D14" t="n">
-        <v>0.25</v>
+        <v>0.0756</v>
       </c>
       <c r="E14" t="n">
         <v>0.9</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.5255</v>
+        <v>-0.6441</v>
       </c>
       <c r="G14" t="n">
-        <v>1.0255</v>
+        <v>0.7952</v>
       </c>
       <c r="H14" t="b">
         <v>0</v>
@@ -9120,16 +9120,16 @@
         <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0886</v>
+        <v>0.2465</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9</v>
+        <v>0.7923</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.506</v>
+        <v>-0.3052</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6831</v>
+        <v>0.7983</v>
       </c>
       <c r="H15" t="b">
         <v>0</v>
@@ -9146,16 +9146,16 @@
         <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0493</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="E16" t="n">
         <v>0.9</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.5155999999999999</v>
+        <v>-0.4334</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6142</v>
+        <v>0.615</v>
       </c>
       <c r="H16" t="b">
         <v>0</v>
@@ -9172,16 +9172,16 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2819</v>
+        <v>0.1354</v>
       </c>
       <c r="E17" t="n">
         <v>0.9</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.5322</v>
+        <v>-0.6201</v>
       </c>
       <c r="G17" t="n">
-        <v>1.096</v>
+        <v>0.8909</v>
       </c>
       <c r="H17" t="b">
         <v>0</v>
@@ -9198,16 +9198,16 @@
         <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3609</v>
+        <v>-0.0736</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5019</v>
+        <v>0.9</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.9555</v>
+        <v>-0.6253</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2336</v>
+        <v>0.4781</v>
       </c>
       <c r="H18" t="b">
         <v>0</v>
@@ -9224,16 +9224,16 @@
         <v>7</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1262</v>
+        <v>-0.1796</v>
       </c>
       <c r="E19" t="n">
         <v>0.9</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.9403</v>
+        <v>-0.9351</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6879</v>
+        <v>0.5759</v>
       </c>
       <c r="H19" t="b">
         <v>0</v>
@@ -9250,16 +9250,16 @@
         <v>8</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.08649999999999999</v>
+        <v>-0.1782</v>
       </c>
       <c r="E20" t="n">
         <v>0.9</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7871</v>
+        <v>-0.8284</v>
       </c>
       <c r="G20" t="n">
-        <v>0.6142</v>
+        <v>0.472</v>
       </c>
       <c r="H20" t="b">
         <v>0</v>
@@ -9276,16 +9276,16 @@
         <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0392</v>
+        <v>-0.1558</v>
       </c>
       <c r="E21" t="n">
         <v>0.9</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.6541</v>
+        <v>-0.7262999999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>0.5756</v>
+        <v>0.4148</v>
       </c>
       <c r="H21" t="b">
         <v>0</v>
@@ -9302,16 +9302,16 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1934</v>
+        <v>-0.1111</v>
       </c>
       <c r="E22" t="n">
         <v>0.9</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6562</v>
+        <v>-0.8995</v>
       </c>
       <c r="G22" t="n">
-        <v>1.0429</v>
+        <v>0.6772</v>
       </c>
       <c r="H22" t="b">
         <v>0</v>
@@ -9328,16 +9328,16 @@
         <v>6</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4495</v>
+        <v>-0.3201</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3295</v>
+        <v>0.6286</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.0917</v>
+        <v>-0.9161</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1927</v>
+        <v>0.2758</v>
       </c>
       <c r="H23" t="b">
         <v>0</v>
@@ -9354,16 +9354,16 @@
         <v>7</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2148</v>
+        <v>-0.4261</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9</v>
+        <v>0.6225000000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.0643</v>
+        <v>-1.2145</v>
       </c>
       <c r="G24" t="n">
-        <v>0.6348</v>
+        <v>0.3622</v>
       </c>
       <c r="H24" t="b">
         <v>0</v>
@@ -9380,16 +9380,16 @@
         <v>8</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.175</v>
+        <v>-0.4247</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9</v>
+        <v>0.4831</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.9165</v>
+        <v>-1.1129</v>
       </c>
       <c r="G25" t="n">
-        <v>0.5665</v>
+        <v>0.2634</v>
       </c>
       <c r="H25" t="b">
         <v>0</v>
@@ -9406,16 +9406,16 @@
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>0.2326</v>
+        <v>0.0446</v>
       </c>
       <c r="E26" t="n">
         <v>0.9</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.5965</v>
+        <v>-0.7247</v>
       </c>
       <c r="G26" t="n">
-        <v>1.0616</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="H26" t="b">
         <v>0</v>
@@ -9432,16 +9432,16 @@
         <v>6</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4103</v>
+        <v>-0.1644</v>
       </c>
       <c r="E27" t="n">
-        <v>0.3882</v>
+        <v>0.9</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.0251</v>
+        <v>-0.7349</v>
       </c>
       <c r="G27" t="n">
-        <v>0.2046</v>
+        <v>0.4062</v>
       </c>
       <c r="H27" t="b">
         <v>0</v>
@@ -9458,16 +9458,16 @@
         <v>7</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.1755</v>
+        <v>-0.2704</v>
       </c>
       <c r="E28" t="n">
         <v>0.9</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.0046</v>
+        <v>-1.0397</v>
       </c>
       <c r="G28" t="n">
-        <v>0.6535</v>
+        <v>0.499</v>
       </c>
       <c r="H28" t="b">
         <v>0</v>
@@ -9484,16 +9484,16 @@
         <v>8</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.1358</v>
+        <v>-0.269</v>
       </c>
       <c r="E29" t="n">
-        <v>0.9</v>
+        <v>0.8704</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.8538</v>
+        <v>-0.9353</v>
       </c>
       <c r="G29" t="n">
-        <v>0.5822000000000001</v>
+        <v>0.3973</v>
       </c>
       <c r="H29" t="b">
         <v>0</v>
@@ -9510,16 +9510,16 @@
         <v>6</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6429</v>
+        <v>-0.209</v>
       </c>
       <c r="E30" t="n">
-        <v>0.2435</v>
+        <v>0.9</v>
       </c>
       <c r="F30" t="n">
-        <v>-1.4924</v>
+        <v>-0.9973</v>
       </c>
       <c r="G30" t="n">
-        <v>0.2067</v>
+        <v>0.5794</v>
       </c>
       <c r="H30" t="b">
         <v>0</v>
@@ -9536,16 +9536,16 @@
         <v>7</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.4081</v>
+        <v>-0.315</v>
       </c>
       <c r="E31" t="n">
-        <v>0.8736</v>
+        <v>0.9</v>
       </c>
       <c r="F31" t="n">
-        <v>-1.4235</v>
+        <v>-1.2572</v>
       </c>
       <c r="G31" t="n">
-        <v>0.6073</v>
+        <v>0.6273</v>
       </c>
       <c r="H31" t="b">
         <v>0</v>
@@ -9562,16 +9562,16 @@
         <v>8</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.3684</v>
+        <v>-0.3136</v>
       </c>
       <c r="E32" t="n">
-        <v>0.8818</v>
+        <v>0.9</v>
       </c>
       <c r="F32" t="n">
-        <v>-1.2953</v>
+        <v>-1.1738</v>
       </c>
       <c r="G32" t="n">
-        <v>0.5585</v>
+        <v>0.5466</v>
       </c>
       <c r="H32" t="b">
         <v>0</v>
@@ -9588,16 +9588,16 @@
         <v>7</v>
       </c>
       <c r="D33" t="n">
-        <v>0.2348</v>
+        <v>-0.106</v>
       </c>
       <c r="E33" t="n">
         <v>0.9</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.6148</v>
+        <v>-0.8944</v>
       </c>
       <c r="G33" t="n">
-        <v>1.0843</v>
+        <v>0.6823</v>
       </c>
       <c r="H33" t="b">
         <v>0</v>
@@ -9614,16 +9614,16 @@
         <v>8</v>
       </c>
       <c r="D34" t="n">
-        <v>0.2745</v>
+        <v>-0.1046</v>
       </c>
       <c r="E34" t="n">
         <v>0.9</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.467</v>
+        <v>-0.7927999999999999</v>
       </c>
       <c r="G34" t="n">
-        <v>1.016</v>
+        <v>0.5835</v>
       </c>
       <c r="H34" t="b">
         <v>0</v>
@@ -9640,16 +9640,16 @@
         <v>8</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0397</v>
+        <v>0.0014</v>
       </c>
       <c r="E35" t="n">
         <v>0.9</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.8872</v>
+        <v>-0.8588</v>
       </c>
       <c r="G35" t="n">
-        <v>0.9666</v>
+        <v>0.8615</v>
       </c>
       <c r="H35" t="b">
         <v>0</v>
@@ -9721,16 +9721,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.3455</v>
+        <v>-0.6439</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6666</v>
+        <v>0.3205</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.9063</v>
+        <v>-1.9436</v>
       </c>
       <c r="G2" t="n">
-        <v>1.2153</v>
+        <v>0.6558</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
@@ -9751,16 +9751,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.709</v>
+        <v>0.9224</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8339</v>
+        <v>0.6536</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.4535</v>
+        <v>-1.6927</v>
       </c>
       <c r="G3" t="n">
-        <v>3.8715</v>
+        <v>3.5375</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
@@ -9781,16 +9781,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.5104</v>
+        <v>1.6302</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3597</v>
+        <v>0.1821</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.1655</v>
+        <v>-0.5825</v>
       </c>
       <c r="G4" t="n">
-        <v>4.1863</v>
+        <v>3.8429</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
@@ -9811,16 +9811,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.8014</v>
+        <v>0.7078</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6687</v>
+        <v>0.636</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.5424</v>
+        <v>-1.2303</v>
       </c>
       <c r="G5" t="n">
-        <v>3.1452</v>
+        <v>2.6459</v>
       </c>
       <c r="H5" t="b">
         <v>0</v>
@@ -9841,19 +9841,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.5772</v>
+        <v>0.9233</v>
       </c>
       <c r="E6" t="n">
-        <v>0.035</v>
+        <v>0.1508</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1181</v>
+        <v>-0.3543</v>
       </c>
       <c r="G6" t="n">
-        <v>3.0363</v>
+        <v>2.201</v>
       </c>
       <c r="H6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -9871,16 +9871,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.2745</v>
+        <v>0.7059</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7403999999999999</v>
+        <v>0.2884</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.3306</v>
+        <v>-0.626</v>
       </c>
       <c r="G7" t="n">
-        <v>1.8796</v>
+        <v>2.0379</v>
       </c>
       <c r="H7" t="b">
         <v>0</v>
@@ -9897,16 +9897,16 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2874</v>
+        <v>-0.1753</v>
       </c>
       <c r="E8" t="n">
         <v>0.9</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.777</v>
+        <v>-3.8205</v>
       </c>
       <c r="G8" t="n">
-        <v>4.3519</v>
+        <v>3.4699</v>
       </c>
       <c r="H8" t="b">
         <v>0</v>
@@ -9923,16 +9923,16 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>2.6332</v>
+        <v>2.1045</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5051</v>
+        <v>0.6245000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.7168</v>
+        <v>-1.7968</v>
       </c>
       <c r="G9" t="n">
-        <v>6.9832</v>
+        <v>6.0058</v>
       </c>
       <c r="H9" t="b">
         <v>0</v>
@@ -9949,16 +9949,16 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>3.0471</v>
+        <v>1.31</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2852</v>
+        <v>0.9</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.1387</v>
+        <v>-2.4441</v>
       </c>
       <c r="G10" t="n">
-        <v>7.2328</v>
+        <v>5.064</v>
       </c>
       <c r="H10" t="b">
         <v>0</v>
@@ -9975,16 +9975,16 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>2.355</v>
+        <v>0.7892</v>
       </c>
       <c r="E11" t="n">
-        <v>0.8421</v>
+        <v>0.9</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.2608</v>
+        <v>-4.2474</v>
       </c>
       <c r="G11" t="n">
-        <v>7.9708</v>
+        <v>5.8258</v>
       </c>
       <c r="H11" t="b">
         <v>0</v>
@@ -10001,16 +10001,16 @@
         <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0654</v>
+        <v>-0.2149</v>
       </c>
       <c r="E12" t="n">
         <v>0.9</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.2846</v>
+        <v>-4.1162</v>
       </c>
       <c r="G12" t="n">
-        <v>4.4153</v>
+        <v>3.6864</v>
       </c>
       <c r="H12" t="b">
         <v>0</v>
@@ -10027,16 +10027,16 @@
         <v>7</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.466</v>
+        <v>-0.6532</v>
       </c>
       <c r="E13" t="n">
         <v>0.9</v>
       </c>
       <c r="F13" t="n">
-        <v>-6.0818</v>
+        <v>-5.6898</v>
       </c>
       <c r="G13" t="n">
-        <v>5.1497</v>
+        <v>4.3834</v>
       </c>
       <c r="H13" t="b">
         <v>0</v>
@@ -10053,16 +10053,16 @@
         <v>8</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3283</v>
+        <v>-0.9819</v>
       </c>
       <c r="E14" t="n">
         <v>0.9</v>
       </c>
       <c r="F14" t="n">
-        <v>-4.6244</v>
+        <v>-5.4238</v>
       </c>
       <c r="G14" t="n">
-        <v>5.2809</v>
+        <v>3.4599</v>
       </c>
       <c r="H14" t="b">
         <v>0</v>
@@ -10079,16 +10079,16 @@
         <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>2.3457</v>
+        <v>2.2798</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4821</v>
+        <v>0.3841</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.4512</v>
+        <v>-1.1256</v>
       </c>
       <c r="G15" t="n">
-        <v>6.1427</v>
+        <v>5.6851</v>
       </c>
       <c r="H15" t="b">
         <v>0</v>
@@ -10105,16 +10105,16 @@
         <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>2.7596</v>
+        <v>1.4853</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2327</v>
+        <v>0.7702</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.8481</v>
+        <v>-1.7503</v>
       </c>
       <c r="G16" t="n">
-        <v>6.3673</v>
+        <v>4.7208</v>
       </c>
       <c r="H16" t="b">
         <v>0</v>
@@ -10131,16 +10131,16 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>2.0675</v>
+        <v>0.9645</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8814</v>
+        <v>0.9</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.1317</v>
+        <v>-3.6985</v>
       </c>
       <c r="G17" t="n">
-        <v>7.2668</v>
+        <v>5.6274</v>
       </c>
       <c r="H17" t="b">
         <v>0</v>
@@ -10157,16 +10157,16 @@
         <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2221</v>
+        <v>-0.0397</v>
       </c>
       <c r="E18" t="n">
         <v>0.9</v>
       </c>
       <c r="F18" t="n">
-        <v>-4.019</v>
+        <v>-3.445</v>
       </c>
       <c r="G18" t="n">
-        <v>3.5749</v>
+        <v>3.3657</v>
       </c>
       <c r="H18" t="b">
         <v>0</v>
@@ -10183,16 +10183,16 @@
         <v>7</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.4779</v>
       </c>
       <c r="E19" t="n">
         <v>0.9</v>
       </c>
       <c r="F19" t="n">
-        <v>-5.9527</v>
+        <v>-5.1409</v>
       </c>
       <c r="G19" t="n">
-        <v>4.4457</v>
+        <v>4.185</v>
       </c>
       <c r="H19" t="b">
         <v>0</v>
@@ -10209,16 +10209,16 @@
         <v>8</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0408</v>
+        <v>-0.8066</v>
       </c>
       <c r="E20" t="n">
         <v>0.9</v>
       </c>
       <c r="F20" t="n">
-        <v>-4.4339</v>
+        <v>-4.8199</v>
       </c>
       <c r="G20" t="n">
-        <v>4.5156</v>
+        <v>3.2066</v>
       </c>
       <c r="H20" t="b">
         <v>0</v>
@@ -10235,16 +10235,16 @@
         <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>0.4139</v>
+        <v>-0.7945</v>
       </c>
       <c r="E21" t="n">
         <v>0.9</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.5127</v>
+        <v>-4.3161</v>
       </c>
       <c r="G21" t="n">
-        <v>4.3405</v>
+        <v>2.7271</v>
       </c>
       <c r="H21" t="b">
         <v>0</v>
@@ -10261,16 +10261,16 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2782</v>
+        <v>-1.3153</v>
       </c>
       <c r="E22" t="n">
         <v>0.9</v>
       </c>
       <c r="F22" t="n">
-        <v>-5.7036</v>
+        <v>-6.1811</v>
       </c>
       <c r="G22" t="n">
-        <v>5.1472</v>
+        <v>3.5505</v>
       </c>
       <c r="H22" t="b">
         <v>0</v>
@@ -10287,16 +10287,16 @@
         <v>6</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.5678</v>
+        <v>-2.3195</v>
       </c>
       <c r="E23" t="n">
-        <v>0.4664</v>
+        <v>0.4579</v>
       </c>
       <c r="F23" t="n">
-        <v>-6.669</v>
+        <v>-5.9976</v>
       </c>
       <c r="G23" t="n">
-        <v>1.5334</v>
+        <v>1.3587</v>
       </c>
       <c r="H23" t="b">
         <v>0</v>
@@ -10313,16 +10313,16 @@
         <v>7</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.0992</v>
+        <v>-2.7577</v>
       </c>
       <c r="E24" t="n">
-        <v>0.5669</v>
+        <v>0.575</v>
       </c>
       <c r="F24" t="n">
-        <v>-8.5246</v>
+        <v>-7.6235</v>
       </c>
       <c r="G24" t="n">
-        <v>2.3261</v>
+        <v>2.1081</v>
       </c>
       <c r="H24" t="b">
         <v>0</v>
@@ -10339,16 +10339,16 @@
         <v>8</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.3049</v>
+        <v>-3.0864</v>
       </c>
       <c r="E25" t="n">
-        <v>0.72</v>
+        <v>0.2871</v>
       </c>
       <c r="F25" t="n">
-        <v>-7.0406</v>
+        <v>-7.3337</v>
       </c>
       <c r="G25" t="n">
-        <v>2.4307</v>
+        <v>1.1608</v>
       </c>
       <c r="H25" t="b">
         <v>0</v>
@@ -10365,16 +10365,16 @@
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.6921</v>
+        <v>-0.5208</v>
       </c>
       <c r="E26" t="n">
         <v>0.9</v>
       </c>
       <c r="F26" t="n">
-        <v>-5.9867</v>
+        <v>-5.2693</v>
       </c>
       <c r="G26" t="n">
-        <v>4.6026</v>
+        <v>4.2278</v>
       </c>
       <c r="H26" t="b">
         <v>0</v>
@@ -10391,16 +10391,16 @@
         <v>6</v>
       </c>
       <c r="D27" t="n">
-        <v>-2.9817</v>
+        <v>-1.5249</v>
       </c>
       <c r="E27" t="n">
-        <v>0.2399</v>
+        <v>0.8173</v>
       </c>
       <c r="F27" t="n">
-        <v>-6.9083</v>
+        <v>-5.0465</v>
       </c>
       <c r="G27" t="n">
-        <v>0.9449</v>
+        <v>1.9967</v>
       </c>
       <c r="H27" t="b">
         <v>0</v>
@@ -10417,16 +10417,16 @@
         <v>7</v>
       </c>
       <c r="D28" t="n">
-        <v>-3.5131</v>
+        <v>-1.9632</v>
       </c>
       <c r="E28" t="n">
-        <v>0.3952</v>
+        <v>0.8528</v>
       </c>
       <c r="F28" t="n">
-        <v>-8.807700000000001</v>
+        <v>-6.7117</v>
       </c>
       <c r="G28" t="n">
-        <v>1.7815</v>
+        <v>2.7853</v>
       </c>
       <c r="H28" t="b">
         <v>0</v>
@@ -10443,16 +10443,16 @@
         <v>8</v>
       </c>
       <c r="D29" t="n">
-        <v>-2.7188</v>
+        <v>-2.2919</v>
       </c>
       <c r="E29" t="n">
-        <v>0.5276</v>
+        <v>0.5921</v>
       </c>
       <c r="F29" t="n">
-        <v>-7.3041</v>
+        <v>-6.4043</v>
       </c>
       <c r="G29" t="n">
-        <v>1.8665</v>
+        <v>1.8204</v>
       </c>
       <c r="H29" t="b">
         <v>0</v>
@@ -10469,16 +10469,16 @@
         <v>6</v>
       </c>
       <c r="D30" t="n">
-        <v>-2.2896</v>
+        <v>-1.0041</v>
       </c>
       <c r="E30" t="n">
-        <v>0.8372000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="F30" t="n">
-        <v>-7.715</v>
+        <v>-5.8699</v>
       </c>
       <c r="G30" t="n">
-        <v>3.1357</v>
+        <v>3.8617</v>
       </c>
       <c r="H30" t="b">
         <v>0</v>
@@ -10495,16 +10495,16 @@
         <v>7</v>
       </c>
       <c r="D31" t="n">
-        <v>-2.821</v>
+        <v>-1.4424</v>
       </c>
       <c r="E31" t="n">
-        <v>0.8136</v>
+        <v>0.9</v>
       </c>
       <c r="F31" t="n">
-        <v>-9.3056</v>
+        <v>-7.2582</v>
       </c>
       <c r="G31" t="n">
-        <v>3.6635</v>
+        <v>4.3733</v>
       </c>
       <c r="H31" t="b">
         <v>0</v>
@@ -10521,16 +10521,16 @@
         <v>8</v>
       </c>
       <c r="D32" t="n">
-        <v>-2.0267</v>
+        <v>-1.7711</v>
       </c>
       <c r="E32" t="n">
         <v>0.9</v>
       </c>
       <c r="F32" t="n">
-        <v>-7.9463</v>
+        <v>-7.0801</v>
       </c>
       <c r="G32" t="n">
-        <v>3.8928</v>
+        <v>3.5379</v>
       </c>
       <c r="H32" t="b">
         <v>0</v>
@@ -10547,16 +10547,16 @@
         <v>7</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.5314</v>
+        <v>-0.4383</v>
       </c>
       <c r="E33" t="n">
         <v>0.9</v>
       </c>
       <c r="F33" t="n">
-        <v>-5.9568</v>
+        <v>-5.3041</v>
       </c>
       <c r="G33" t="n">
-        <v>4.894</v>
+        <v>4.4275</v>
       </c>
       <c r="H33" t="b">
         <v>0</v>
@@ -10573,16 +10573,16 @@
         <v>8</v>
       </c>
       <c r="D34" t="n">
-        <v>0.2629</v>
+        <v>-0.767</v>
       </c>
       <c r="E34" t="n">
         <v>0.9</v>
       </c>
       <c r="F34" t="n">
-        <v>-4.4727</v>
+        <v>-5.0142</v>
       </c>
       <c r="G34" t="n">
-        <v>4.9985</v>
+        <v>3.4802</v>
       </c>
       <c r="H34" t="b">
         <v>0</v>
@@ -10599,16 +10599,16 @@
         <v>8</v>
       </c>
       <c r="D35" t="n">
-        <v>0.7943</v>
+        <v>-0.3287</v>
       </c>
       <c r="E35" t="n">
         <v>0.9</v>
       </c>
       <c r="F35" t="n">
-        <v>-5.1252</v>
+        <v>-5.6377</v>
       </c>
       <c r="G35" t="n">
-        <v>6.7139</v>
+        <v>4.9803</v>
       </c>
       <c r="H35" t="b">
         <v>0</v>
@@ -10680,16 +10680,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-12.4544</v>
+        <v>-4.0276</v>
       </c>
       <c r="E2" t="n">
-        <v>0.262</v>
+        <v>0.768</v>
       </c>
       <c r="F2" t="n">
-        <v>-34.6711</v>
+        <v>-30.4947</v>
       </c>
       <c r="G2" t="n">
-        <v>9.7623</v>
+        <v>22.4395</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
@@ -10710,16 +10710,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>21.3845</v>
+        <v>-26.4202</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4952</v>
+        <v>0.461</v>
       </c>
       <c r="F3" t="n">
-        <v>-24.5476</v>
+        <v>-80.3843</v>
       </c>
       <c r="G3" t="n">
-        <v>67.31659999999999</v>
+        <v>27.5438</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
@@ -10740,16 +10740,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2.8362</v>
+        <v>-22.4043</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9</v>
+        <v>0.4595</v>
       </c>
       <c r="F4" t="n">
-        <v>-36.0276</v>
+        <v>-68.06399999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>41.7</v>
+        <v>23.2554</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
@@ -10770,16 +10770,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-18.5483</v>
+        <v>4.0159</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3851</v>
+        <v>0.9</v>
       </c>
       <c r="F5" t="n">
-        <v>-52.589</v>
+        <v>-35.9773</v>
       </c>
       <c r="G5" t="n">
-        <v>15.4924</v>
+        <v>44.0092</v>
       </c>
       <c r="H5" t="b">
         <v>0</v>
@@ -10800,16 +10800,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.2216</v>
+        <v>17.1471</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9</v>
+        <v>0.1849</v>
       </c>
       <c r="F6" t="n">
-        <v>-22.8863</v>
+        <v>-8.6305</v>
       </c>
       <c r="G6" t="n">
-        <v>22.4431</v>
+        <v>42.9247</v>
       </c>
       <c r="H6" t="b">
         <v>0</v>
@@ -10830,16 +10830,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-5.5228</v>
+        <v>6.8468</v>
       </c>
       <c r="E7" t="n">
-        <v>0.642</v>
+        <v>0.6209</v>
       </c>
       <c r="F7" t="n">
-        <v>-28.7168</v>
+        <v>-20.2667</v>
       </c>
       <c r="G7" t="n">
-        <v>17.6713</v>
+        <v>33.9602</v>
       </c>
       <c r="H7" t="b">
         <v>0</v>
@@ -10856,16 +10856,16 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>-32.4293</v>
+        <v>-47.3825</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6189</v>
+        <v>0.4534</v>
       </c>
       <c r="F8" t="n">
-        <v>-92.20350000000001</v>
+        <v>-122.2431</v>
       </c>
       <c r="G8" t="n">
-        <v>27.3449</v>
+        <v>27.4781</v>
       </c>
       <c r="H8" t="b">
         <v>0</v>
@@ -10882,16 +10882,16 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>-9.4595</v>
+        <v>-16.0296</v>
       </c>
       <c r="E9" t="n">
         <v>0.9</v>
       </c>
       <c r="F9" t="n">
-        <v>-73.43340000000001</v>
+        <v>-96.1498</v>
       </c>
       <c r="G9" t="n">
-        <v>54.5144</v>
+        <v>64.0907</v>
       </c>
       <c r="H9" t="b">
         <v>0</v>
@@ -10908,16 +10908,16 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>-7.7077</v>
+        <v>-17.6844</v>
       </c>
       <c r="E10" t="n">
         <v>0.9</v>
       </c>
       <c r="F10" t="n">
-        <v>-69.2666</v>
+        <v>-94.78019999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>53.8511</v>
+        <v>59.4113</v>
       </c>
       <c r="H10" t="b">
         <v>0</v>
@@ -10934,16 +10934,16 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>-40.7085</v>
+        <v>-49.7801</v>
       </c>
       <c r="E11" t="n">
-        <v>0.7088</v>
+        <v>0.7299</v>
       </c>
       <c r="F11" t="n">
-        <v>-123.2984</v>
+        <v>-153.2149</v>
       </c>
       <c r="G11" t="n">
-        <v>41.8814</v>
+        <v>53.6547</v>
       </c>
       <c r="H11" t="b">
         <v>0</v>
@@ -10960,16 +10960,16 @@
         <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>21.8525</v>
+        <v>-18.6695</v>
       </c>
       <c r="E12" t="n">
         <v>0.9</v>
       </c>
       <c r="F12" t="n">
-        <v>-42.1214</v>
+        <v>-98.7898</v>
       </c>
       <c r="G12" t="n">
-        <v>85.8263</v>
+        <v>61.4507</v>
       </c>
       <c r="H12" t="b">
         <v>0</v>
@@ -10986,16 +10986,16 @@
         <v>7</v>
       </c>
       <c r="D13" t="n">
-        <v>-30.4118</v>
+        <v>-19.642</v>
       </c>
       <c r="E13" t="n">
         <v>0.9</v>
       </c>
       <c r="F13" t="n">
-        <v>-113.0017</v>
+        <v>-123.0768</v>
       </c>
       <c r="G13" t="n">
-        <v>52.1781</v>
+        <v>83.7928</v>
       </c>
       <c r="H13" t="b">
         <v>0</v>
@@ -11012,16 +11012,16 @@
         <v>8</v>
       </c>
       <c r="D14" t="n">
-        <v>-8.7364</v>
+        <v>11.1979</v>
       </c>
       <c r="E14" t="n">
         <v>0.9</v>
       </c>
       <c r="F14" t="n">
-        <v>-81.57389999999999</v>
+        <v>-80.023</v>
       </c>
       <c r="G14" t="n">
-        <v>64.101</v>
+        <v>102.4188</v>
       </c>
       <c r="H14" t="b">
         <v>0</v>
@@ -11038,16 +11038,16 @@
         <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>22.9698</v>
+        <v>31.3529</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8566</v>
+        <v>0.7896</v>
       </c>
       <c r="F15" t="n">
-        <v>-32.8711</v>
+        <v>-38.5817</v>
       </c>
       <c r="G15" t="n">
-        <v>78.8108</v>
+        <v>101.2876</v>
       </c>
       <c r="H15" t="b">
         <v>0</v>
@@ -11064,16 +11064,16 @@
         <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>24.7216</v>
+        <v>29.6981</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7577</v>
+        <v>0.7921</v>
       </c>
       <c r="F16" t="n">
-        <v>-28.3355</v>
+        <v>-36.7501</v>
       </c>
       <c r="G16" t="n">
-        <v>77.7787</v>
+        <v>96.14619999999999</v>
       </c>
       <c r="H16" t="b">
         <v>0</v>
@@ -11090,16 +11090,16 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>-8.279199999999999</v>
+        <v>-2.3976</v>
       </c>
       <c r="E17" t="n">
         <v>0.9</v>
       </c>
       <c r="F17" t="n">
-        <v>-84.7426</v>
+        <v>-98.1596</v>
       </c>
       <c r="G17" t="n">
-        <v>68.1842</v>
+        <v>93.3644</v>
       </c>
       <c r="H17" t="b">
         <v>0</v>
@@ -11116,16 +11116,16 @@
         <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>54.2818</v>
+        <v>28.713</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0612</v>
+        <v>0.858</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.5592</v>
+        <v>-41.2217</v>
       </c>
       <c r="G18" t="n">
-        <v>110.1228</v>
+        <v>98.6476</v>
       </c>
       <c r="H18" t="b">
         <v>0</v>
@@ -11142,16 +11142,16 @@
         <v>7</v>
       </c>
       <c r="D19" t="n">
-        <v>2.0175</v>
+        <v>27.7405</v>
       </c>
       <c r="E19" t="n">
         <v>0.9</v>
       </c>
       <c r="F19" t="n">
-        <v>-74.44589999999999</v>
+        <v>-68.0215</v>
       </c>
       <c r="G19" t="n">
-        <v>78.48090000000001</v>
+        <v>123.5025</v>
       </c>
       <c r="H19" t="b">
         <v>0</v>
@@ -11168,16 +11168,16 @@
         <v>8</v>
       </c>
       <c r="D20" t="n">
-        <v>23.6929</v>
+        <v>58.5804</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9</v>
+        <v>0.312</v>
       </c>
       <c r="F20" t="n">
-        <v>-42.1163</v>
+        <v>-23.8384</v>
       </c>
       <c r="G20" t="n">
-        <v>89.5021</v>
+        <v>140.9992</v>
       </c>
       <c r="H20" t="b">
         <v>0</v>
@@ -11194,16 +11194,16 @@
         <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>1.7517</v>
+        <v>-1.6549</v>
       </c>
       <c r="E21" t="n">
         <v>0.9</v>
       </c>
       <c r="F21" t="n">
-        <v>-55.9956</v>
+        <v>-73.97709999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>59.4991</v>
+        <v>70.6673</v>
       </c>
       <c r="H21" t="b">
         <v>0</v>
@@ -11220,16 +11220,16 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>-31.249</v>
+        <v>-33.7506</v>
       </c>
       <c r="E22" t="n">
-        <v>0.8923</v>
+        <v>0.9</v>
       </c>
       <c r="F22" t="n">
-        <v>-111.0384</v>
+        <v>-133.6781</v>
       </c>
       <c r="G22" t="n">
-        <v>48.5404</v>
+        <v>66.1769</v>
       </c>
       <c r="H22" t="b">
         <v>0</v>
@@ -11246,16 +11246,16 @@
         <v>6</v>
       </c>
       <c r="D23" t="n">
-        <v>31.3119</v>
+        <v>-2.64</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6613</v>
+        <v>0.9</v>
       </c>
       <c r="F23" t="n">
-        <v>-29.0032</v>
+        <v>-78.1781</v>
       </c>
       <c r="G23" t="n">
-        <v>91.6271</v>
+        <v>72.8981</v>
       </c>
       <c r="H23" t="b">
         <v>0</v>
@@ -11272,16 +11272,16 @@
         <v>7</v>
       </c>
       <c r="D24" t="n">
-        <v>-20.9523</v>
+        <v>-3.6124</v>
       </c>
       <c r="E24" t="n">
         <v>0.9</v>
       </c>
       <c r="F24" t="n">
-        <v>-100.7418</v>
+        <v>-103.5399</v>
       </c>
       <c r="G24" t="n">
-        <v>58.8371</v>
+        <v>96.3151</v>
       </c>
       <c r="H24" t="b">
         <v>0</v>
@@ -11298,16 +11298,16 @@
         <v>8</v>
       </c>
       <c r="D25" t="n">
-        <v>0.7231</v>
+        <v>27.2275</v>
       </c>
       <c r="E25" t="n">
         <v>0.9</v>
       </c>
       <c r="F25" t="n">
-        <v>-68.9229</v>
+        <v>-59.9964</v>
       </c>
       <c r="G25" t="n">
-        <v>70.369</v>
+        <v>114.4513</v>
       </c>
       <c r="H25" t="b">
         <v>0</v>
@@ -11324,16 +11324,16 @@
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>-33.0007</v>
+        <v>-32.0957</v>
       </c>
       <c r="E26" t="n">
-        <v>0.834</v>
+        <v>0.9</v>
       </c>
       <c r="F26" t="n">
-        <v>-110.8673</v>
+        <v>-129.6149</v>
       </c>
       <c r="G26" t="n">
-        <v>44.8658</v>
+        <v>65.4235</v>
       </c>
       <c r="H26" t="b">
         <v>0</v>
@@ -11350,16 +11350,16 @@
         <v>6</v>
       </c>
       <c r="D27" t="n">
-        <v>29.5602</v>
+        <v>-0.9851</v>
       </c>
       <c r="E27" t="n">
-        <v>0.6744</v>
+        <v>0.9</v>
       </c>
       <c r="F27" t="n">
-        <v>-28.1871</v>
+        <v>-73.3073</v>
       </c>
       <c r="G27" t="n">
-        <v>87.30759999999999</v>
+        <v>71.33710000000001</v>
       </c>
       <c r="H27" t="b">
         <v>0</v>
@@ -11376,16 +11376,16 @@
         <v>7</v>
       </c>
       <c r="D28" t="n">
-        <v>-22.7041</v>
+        <v>-1.9575</v>
       </c>
       <c r="E28" t="n">
         <v>0.9</v>
       </c>
       <c r="F28" t="n">
-        <v>-100.5706</v>
+        <v>-99.4768</v>
       </c>
       <c r="G28" t="n">
-        <v>55.1624</v>
+        <v>95.5617</v>
       </c>
       <c r="H28" t="b">
         <v>0</v>
@@ -11402,16 +11402,16 @@
         <v>8</v>
       </c>
       <c r="D29" t="n">
-        <v>-1.0287</v>
+        <v>28.8823</v>
       </c>
       <c r="E29" t="n">
         <v>0.9</v>
       </c>
       <c r="F29" t="n">
-        <v>-68.4631</v>
+        <v>-55.5718</v>
       </c>
       <c r="G29" t="n">
-        <v>66.4057</v>
+        <v>113.3365</v>
       </c>
       <c r="H29" t="b">
         <v>0</v>
@@ -11428,16 +11428,16 @@
         <v>6</v>
       </c>
       <c r="D30" t="n">
-        <v>62.561</v>
+        <v>31.1106</v>
       </c>
       <c r="E30" t="n">
-        <v>0.2084</v>
+        <v>0.9</v>
       </c>
       <c r="F30" t="n">
-        <v>-17.2285</v>
+        <v>-68.8169</v>
       </c>
       <c r="G30" t="n">
-        <v>142.3504</v>
+        <v>131.0381</v>
       </c>
       <c r="H30" t="b">
         <v>0</v>
@@ -11454,16 +11454,16 @@
         <v>7</v>
       </c>
       <c r="D31" t="n">
-        <v>10.2967</v>
+        <v>30.1381</v>
       </c>
       <c r="E31" t="n">
         <v>0.9</v>
       </c>
       <c r="F31" t="n">
-        <v>-85.06999999999999</v>
+        <v>-89.298</v>
       </c>
       <c r="G31" t="n">
-        <v>105.6633</v>
+        <v>149.5743</v>
       </c>
       <c r="H31" t="b">
         <v>0</v>
@@ -11480,16 +11480,16 @@
         <v>8</v>
       </c>
       <c r="D32" t="n">
-        <v>31.9721</v>
+        <v>60.978</v>
       </c>
       <c r="E32" t="n">
-        <v>0.9</v>
+        <v>0.5885</v>
       </c>
       <c r="F32" t="n">
-        <v>-55.0854</v>
+        <v>-48.0518</v>
       </c>
       <c r="G32" t="n">
-        <v>119.0295</v>
+        <v>170.0079</v>
       </c>
       <c r="H32" t="b">
         <v>0</v>
@@ -11506,16 +11506,16 @@
         <v>7</v>
       </c>
       <c r="D33" t="n">
-        <v>-52.2643</v>
+        <v>-0.9724</v>
       </c>
       <c r="E33" t="n">
-        <v>0.4113</v>
+        <v>0.9</v>
       </c>
       <c r="F33" t="n">
-        <v>-132.0537</v>
+        <v>-100.8999</v>
       </c>
       <c r="G33" t="n">
-        <v>27.5251</v>
+        <v>98.9551</v>
       </c>
       <c r="H33" t="b">
         <v>0</v>
@@ -11532,16 +11532,16 @@
         <v>8</v>
       </c>
       <c r="D34" t="n">
-        <v>-30.5889</v>
+        <v>29.8675</v>
       </c>
       <c r="E34" t="n">
-        <v>0.8061</v>
+        <v>0.9</v>
       </c>
       <c r="F34" t="n">
-        <v>-100.2348</v>
+        <v>-57.3564</v>
       </c>
       <c r="G34" t="n">
-        <v>39.057</v>
+        <v>117.0913</v>
       </c>
       <c r="H34" t="b">
         <v>0</v>
@@ -11558,16 +11558,16 @@
         <v>8</v>
       </c>
       <c r="D35" t="n">
-        <v>21.6754</v>
+        <v>30.8399</v>
       </c>
       <c r="E35" t="n">
         <v>0.9</v>
       </c>
       <c r="F35" t="n">
-        <v>-65.38200000000001</v>
+        <v>-78.18989999999999</v>
       </c>
       <c r="G35" t="n">
-        <v>108.7328</v>
+        <v>139.8697</v>
       </c>
       <c r="H35" t="b">
         <v>0</v>
